--- a/2026/data/GOA_arrowtooth_2026.xlsx
+++ b/2026/data/GOA_arrowtooth_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalei.shotwell\Work\GitHub\GOA-ATF-ESP\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B94128CB-ADEC-49F5-94CA-69D3DA927089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230A647E-B345-4440-A44E-751A718EBD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>
@@ -33,11 +33,24 @@
     <sheet name="diet_data" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="490">
   <si>
     <t>Sheet name</t>
   </si>
@@ -57146,7 +57159,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -57527,7 +57540,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -57582,7 +57595,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1547833.833543</v>
+        <v>1547833.83354299</v>
       </c>
       <c r="I2">
         <v>100045.467677347</v>
@@ -57611,7 +57624,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1629517.296695</v>
+        <v>1629517.29669599</v>
       </c>
       <c r="I3">
         <v>114241.35649547201</v>
@@ -57643,7 +57656,7 @@
         <v>1238474.101674</v>
       </c>
       <c r="I4">
-        <v>98789.224525301703</v>
+        <v>98789.224525301601</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -57698,7 +57711,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2800835.2757049999</v>
+        <v>2800835.2757060002</v>
       </c>
       <c r="I6">
         <v>370586.551029842</v>
@@ -57785,7 +57798,7 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>1763413.103019</v>
+        <v>1763413.103018</v>
       </c>
       <c r="I9">
         <v>158664.005522769</v>
@@ -57875,7 +57888,7 @@
         <v>1656370.286474</v>
       </c>
       <c r="I12">
-        <v>133788.584394423</v>
+        <v>133788.58439442399</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -57930,7 +57943,7 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>1074098.7810169901</v>
+        <v>1074098.7810170001</v>
       </c>
       <c r="I14">
         <v>67256.008133206895</v>
@@ -57988,10 +58001,39 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>1184805.7316650001</v>
+        <v>1184805.7316669901</v>
       </c>
       <c r="I16">
         <v>123992.40768903399</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>2025</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1442690.568153</v>
+      </c>
+      <c r="I17">
+        <v>147241.22555787599</v>
       </c>
     </row>
   </sheetData>
@@ -58001,7 +58043,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
@@ -58418,7 +58460,7 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>17388.130000000016</v>
+        <v>17300.900000000009</v>
       </c>
       <c r="H16">
         <v>0.05</v>
@@ -58444,7 +58486,7 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>21916.17000000002</v>
+        <v>21915.810000000045</v>
       </c>
       <c r="H17">
         <v>0.05</v>
@@ -58470,7 +58512,7 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>19078.320000000003</v>
+        <v>19078.320000000032</v>
       </c>
       <c r="H18">
         <v>0.05</v>
@@ -58496,7 +58538,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>22918.440000000013</v>
+        <v>22918.440000000024</v>
       </c>
       <c r="H19">
         <v>0.05</v>
@@ -58522,7 +58564,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>18278.790000000019</v>
+        <v>18278.790000000037</v>
       </c>
       <c r="H20">
         <v>0.05</v>
@@ -58548,7 +58590,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>22483.679999999968</v>
+        <v>22476.679999999993</v>
       </c>
       <c r="H21">
         <v>0.05</v>
@@ -58600,7 +58642,7 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>12957.910000000029</v>
+        <v>12957.910000000033</v>
       </c>
       <c r="H23">
         <v>0.05</v>
@@ -58626,7 +58668,7 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>16142.020000000102</v>
+        <v>16142.020000000108</v>
       </c>
       <c r="H24">
         <v>0.05</v>
@@ -58652,7 +58694,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>24211.239999999936</v>
+        <v>24211.239999999958</v>
       </c>
       <c r="H25">
         <v>0.05</v>
@@ -58678,7 +58720,7 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>19925.51000000002</v>
+        <v>19925.510000000009</v>
       </c>
       <c r="H26">
         <v>0.05</v>
@@ -58704,7 +58746,7 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>21213.230000000003</v>
+        <v>21213.230000000014</v>
       </c>
       <c r="H27">
         <v>0.05</v>
@@ -58730,7 +58772,7 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>30275.13500000038</v>
+        <v>30253.670000000347</v>
       </c>
       <c r="H28">
         <v>0.05</v>
@@ -58756,7 +58798,7 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>15794.055000000228</v>
+        <v>15757.642000000227</v>
       </c>
       <c r="H29">
         <v>0.05</v>
@@ -58782,7 +58824,7 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>20019.734000000128</v>
+        <v>19989.206000000166</v>
       </c>
       <c r="H30">
         <v>0.05</v>
@@ -58808,7 +58850,7 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>27743.675000000498</v>
+        <v>27739.111000000496</v>
       </c>
       <c r="H31">
         <v>0.05</v>
@@ -58834,7 +58876,7 @@
         <v>1</v>
       </c>
       <c r="G32">
-        <v>25510.175000000509</v>
+        <v>25507.517000000473</v>
       </c>
       <c r="H32">
         <v>0.05</v>
@@ -58860,7 +58902,7 @@
         <v>1</v>
       </c>
       <c r="G33">
-        <v>29272.582000000348</v>
+        <v>29269.818000000345</v>
       </c>
       <c r="H33">
         <v>0.05</v>
@@ -58886,7 +58928,7 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>24914.845000000354</v>
+        <v>24911.85100000029</v>
       </c>
       <c r="H34">
         <v>0.05</v>
@@ -58912,7 +58954,7 @@
         <v>1</v>
       </c>
       <c r="G35">
-        <v>24510.32302842529</v>
+        <v>24496.384927930034</v>
       </c>
       <c r="H35">
         <v>0.05</v>
@@ -58938,7 +58980,7 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>31149.016934668227</v>
+        <v>31139.410542439629</v>
       </c>
       <c r="H36">
         <v>0.05</v>
@@ -58964,7 +59006,7 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>20890.672214942726</v>
+        <v>20886.262853499942</v>
       </c>
       <c r="H37">
         <v>0.05</v>
@@ -58990,7 +59032,7 @@
         <v>1</v>
       </c>
       <c r="G38">
-        <v>21973.275929858184</v>
+        <v>21966.780404421927</v>
       </c>
       <c r="H38">
         <v>0.05</v>
@@ -59016,7 +59058,7 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>36662.335197216031</v>
+        <v>36661.631675450255</v>
       </c>
       <c r="H39">
         <v>0.05</v>
@@ -59042,7 +59084,7 @@
         <v>1</v>
       </c>
       <c r="G40">
-        <v>19419.161857402531</v>
+        <v>19417.957832149852</v>
       </c>
       <c r="H40">
         <v>0.05</v>
@@ -59068,7 +59110,7 @@
         <v>1</v>
       </c>
       <c r="G41">
-        <v>20060.339773541284</v>
+        <v>20056.694251663608</v>
       </c>
       <c r="H41">
         <v>0.05</v>
@@ -59094,7 +59136,7 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>27145.427224491923</v>
+        <v>27143.932184040481</v>
       </c>
       <c r="H42">
         <v>0.05</v>
@@ -59120,7 +59162,7 @@
         <v>1</v>
       </c>
       <c r="G43">
-        <v>18967.562635143164</v>
+        <v>18964.458382597597</v>
       </c>
       <c r="H43">
         <v>0.05</v>
@@ -59146,7 +59188,7 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>24714.950179663061</v>
+        <v>24714.184406504792</v>
       </c>
       <c r="H44">
         <v>0.05</v>
@@ -59172,7 +59214,7 @@
         <v>1</v>
       </c>
       <c r="G45">
-        <v>21244.017519600598</v>
+        <v>21243.079944171859</v>
       </c>
       <c r="H45">
         <v>0.05</v>
@@ -59198,7 +59240,7 @@
         <v>1</v>
       </c>
       <c r="G46">
-        <v>9989.4178943366915</v>
+        <v>9989.0522988863668</v>
       </c>
       <c r="H46">
         <v>0.05</v>
@@ -59224,7 +59266,7 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>11627.894552236996</v>
+        <v>11627.382017870881</v>
       </c>
       <c r="H47">
         <v>0.05</v>
@@ -59250,7 +59292,7 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>9194.022113112067</v>
+        <v>9193.7284773063675</v>
       </c>
       <c r="H48">
         <v>0.05</v>
@@ -59276,7 +59318,7 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>18180.658957255921</v>
+        <v>18182.684685915076</v>
       </c>
       <c r="H49">
         <v>0.05</v>
@@ -59302,9 +59344,35 @@
         <v>1</v>
       </c>
       <c r="G50">
-        <v>11272.024798960918</v>
+        <v>13380.299777241076</v>
       </c>
       <c r="H50">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>2026</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>12621.795976890819</v>
+      </c>
+      <c r="H51">
         <v>0.05</v>
       </c>
     </row>
@@ -59315,7 +59383,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:DU46"/>
+  <dimension ref="A1:DU48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:125" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -61977,10 +62045,10 @@
     </row>
     <row r="17" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -61989,190 +62057,142 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>2005113</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>67063236</v>
       </c>
       <c r="K17">
-        <v>8</v>
+        <v>124578645</v>
       </c>
       <c r="L17">
-        <v>13</v>
+        <v>153139884</v>
       </c>
       <c r="M17">
-        <v>17</v>
+        <v>124858708</v>
       </c>
       <c r="N17">
-        <v>31</v>
+        <v>174252960</v>
       </c>
       <c r="O17">
-        <v>35</v>
+        <v>177782473</v>
       </c>
       <c r="P17">
-        <v>39</v>
+        <v>119555288</v>
       </c>
       <c r="Q17">
-        <v>53</v>
+        <v>78276280</v>
       </c>
       <c r="R17">
-        <v>71</v>
+        <v>68466538</v>
       </c>
       <c r="S17">
-        <v>67</v>
+        <v>49394151</v>
       </c>
       <c r="T17">
-        <v>109</v>
+        <v>37201500</v>
       </c>
       <c r="U17">
-        <v>158</v>
+        <v>19026897</v>
       </c>
       <c r="V17">
-        <v>233</v>
+        <v>8663732</v>
       </c>
       <c r="W17">
-        <v>362</v>
+        <v>7151850</v>
       </c>
       <c r="X17">
-        <v>416</v>
+        <v>1313500</v>
       </c>
       <c r="Y17">
-        <v>464</v>
+        <v>2732842</v>
       </c>
       <c r="Z17">
-        <v>475</v>
+        <v>1721586</v>
       </c>
       <c r="AA17">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>258</v>
+        <v>723063</v>
       </c>
       <c r="AD17">
-        <v>237</v>
+        <v>1387434</v>
       </c>
       <c r="AE17">
-        <v>260</v>
+        <v>37516412</v>
       </c>
       <c r="AF17">
-        <v>168</v>
+        <v>109942536</v>
       </c>
       <c r="AG17">
-        <v>115</v>
+        <v>44064684</v>
       </c>
       <c r="AH17">
-        <v>100</v>
+        <v>111678227</v>
       </c>
       <c r="AI17">
-        <v>89</v>
+        <v>110060250</v>
       </c>
       <c r="AJ17">
-        <v>79</v>
+        <v>124131999</v>
       </c>
       <c r="AK17">
-        <v>105</v>
+        <v>87201355</v>
       </c>
       <c r="AL17">
-        <v>4</v>
+        <v>19311039</v>
       </c>
       <c r="AM17">
-        <v>11</v>
+        <v>24310090</v>
       </c>
       <c r="AN17">
-        <v>5</v>
+        <v>20181442</v>
       </c>
       <c r="AO17">
-        <v>14</v>
+        <v>22954049</v>
       </c>
       <c r="AP17">
-        <v>22</v>
+        <v>1655897</v>
       </c>
       <c r="AQ17">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>39</v>
+        <v>2199841</v>
       </c>
       <c r="AS17">
-        <v>45</v>
+        <v>3192990</v>
       </c>
       <c r="AT17">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>219</v>
-      </c>
-      <c r="AY17">
-        <v>160</v>
-      </c>
-      <c r="AZ17">
-        <v>80</v>
-      </c>
-      <c r="BA17">
-        <v>35</v>
-      </c>
-      <c r="BB17">
-        <v>17</v>
-      </c>
-      <c r="BC17">
-        <v>4</v>
-      </c>
-      <c r="BD17">
-        <v>6</v>
-      </c>
-      <c r="BE17">
-        <v>10</v>
-      </c>
-      <c r="BF17">
-        <v>4</v>
-      </c>
-      <c r="BG17">
-        <v>4</v>
-      </c>
-      <c r="BH17">
-        <v>3</v>
-      </c>
-      <c r="BI17">
-        <v>4</v>
-      </c>
-      <c r="BJ17">
-        <v>5</v>
-      </c>
-      <c r="BK17">
-        <v>0</v>
-      </c>
-      <c r="BL17">
-        <v>3</v>
-      </c>
-      <c r="BM17">
-        <v>3</v>
-      </c>
-      <c r="BN17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:66" x14ac:dyDescent="0.3">
@@ -62192,187 +62212,187 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M18">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N18">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="O18">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="P18">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Q18">
         <v>53</v>
       </c>
       <c r="R18">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="S18">
+        <v>67</v>
+      </c>
+      <c r="T18">
+        <v>109</v>
+      </c>
+      <c r="U18">
+        <v>158</v>
+      </c>
+      <c r="V18">
+        <v>233</v>
+      </c>
+      <c r="W18">
+        <v>362</v>
+      </c>
+      <c r="X18">
+        <v>416</v>
+      </c>
+      <c r="Y18">
+        <v>464</v>
+      </c>
+      <c r="Z18">
+        <v>475</v>
+      </c>
+      <c r="AA18">
+        <v>445</v>
+      </c>
+      <c r="AB18">
+        <v>335</v>
+      </c>
+      <c r="AC18">
+        <v>258</v>
+      </c>
+      <c r="AD18">
+        <v>237</v>
+      </c>
+      <c r="AE18">
+        <v>260</v>
+      </c>
+      <c r="AF18">
+        <v>168</v>
+      </c>
+      <c r="AG18">
+        <v>115</v>
+      </c>
+      <c r="AH18">
+        <v>100</v>
+      </c>
+      <c r="AI18">
+        <v>89</v>
+      </c>
+      <c r="AJ18">
+        <v>79</v>
+      </c>
+      <c r="AK18">
+        <v>105</v>
+      </c>
+      <c r="AL18">
+        <v>4</v>
+      </c>
+      <c r="AM18">
+        <v>11</v>
+      </c>
+      <c r="AN18">
+        <v>5</v>
+      </c>
+      <c r="AO18">
+        <v>14</v>
+      </c>
+      <c r="AP18">
+        <v>22</v>
+      </c>
+      <c r="AQ18">
+        <v>18</v>
+      </c>
+      <c r="AR18">
+        <v>39</v>
+      </c>
+      <c r="AS18">
         <v>45</v>
       </c>
-      <c r="T18">
-        <v>41</v>
-      </c>
-      <c r="U18">
-        <v>44</v>
-      </c>
-      <c r="V18">
-        <v>36</v>
-      </c>
-      <c r="W18">
-        <v>55</v>
-      </c>
-      <c r="X18">
-        <v>68</v>
-      </c>
-      <c r="Y18">
-        <v>70</v>
-      </c>
-      <c r="Z18">
-        <v>70</v>
-      </c>
-      <c r="AA18">
-        <v>60</v>
-      </c>
-      <c r="AB18">
-        <v>45</v>
-      </c>
-      <c r="AC18">
-        <v>31</v>
-      </c>
-      <c r="AD18">
-        <v>28</v>
-      </c>
-      <c r="AE18">
-        <v>32</v>
-      </c>
-      <c r="AF18">
-        <v>20</v>
-      </c>
-      <c r="AG18">
+      <c r="AT18">
+        <v>49</v>
+      </c>
+      <c r="AU18">
+        <v>79</v>
+      </c>
+      <c r="AV18">
+        <v>113</v>
+      </c>
+      <c r="AW18">
+        <v>179</v>
+      </c>
+      <c r="AX18">
+        <v>219</v>
+      </c>
+      <c r="AY18">
+        <v>160</v>
+      </c>
+      <c r="AZ18">
+        <v>80</v>
+      </c>
+      <c r="BA18">
+        <v>35</v>
+      </c>
+      <c r="BB18">
         <v>17</v>
-      </c>
-      <c r="AH18">
-        <v>5</v>
-      </c>
-      <c r="AI18">
-        <v>1</v>
-      </c>
-      <c r="AJ18">
-        <v>4</v>
-      </c>
-      <c r="AK18">
-        <v>5</v>
-      </c>
-      <c r="AL18">
-        <v>1</v>
-      </c>
-      <c r="AM18">
-        <v>2</v>
-      </c>
-      <c r="AN18">
-        <v>7</v>
-      </c>
-      <c r="AO18">
-        <v>7</v>
-      </c>
-      <c r="AP18">
-        <v>10</v>
-      </c>
-      <c r="AQ18">
-        <v>15</v>
-      </c>
-      <c r="AR18">
-        <v>13</v>
-      </c>
-      <c r="AS18">
-        <v>20</v>
-      </c>
-      <c r="AT18">
-        <v>43</v>
-      </c>
-      <c r="AU18">
-        <v>41</v>
-      </c>
-      <c r="AV18">
-        <v>38</v>
-      </c>
-      <c r="AW18">
-        <v>34</v>
-      </c>
-      <c r="AX18">
-        <v>37</v>
-      </c>
-      <c r="AY18">
-        <v>14</v>
-      </c>
-      <c r="AZ18">
-        <v>23</v>
-      </c>
-      <c r="BA18">
-        <v>7</v>
-      </c>
-      <c r="BB18">
-        <v>11</v>
       </c>
       <c r="BC18">
         <v>4</v>
       </c>
       <c r="BD18">
+        <v>6</v>
+      </c>
+      <c r="BE18">
+        <v>10</v>
+      </c>
+      <c r="BF18">
+        <v>4</v>
+      </c>
+      <c r="BG18">
+        <v>4</v>
+      </c>
+      <c r="BH18">
         <v>3</v>
       </c>
-      <c r="BE18">
+      <c r="BI18">
         <v>4</v>
       </c>
-      <c r="BF18">
+      <c r="BJ18">
+        <v>5</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
         <v>3</v>
       </c>
-      <c r="BG18">
-        <v>1</v>
-      </c>
-      <c r="BH18">
-        <v>0</v>
-      </c>
-      <c r="BI18">
-        <v>0</v>
-      </c>
-      <c r="BJ18">
-        <v>0</v>
-      </c>
-      <c r="BK18">
-        <v>0</v>
-      </c>
-      <c r="BL18">
-        <v>0</v>
-      </c>
       <c r="BM18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BN18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:66" x14ac:dyDescent="0.3">
@@ -62392,187 +62412,187 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+      <c r="L19">
+        <v>15</v>
+      </c>
+      <c r="M19">
+        <v>13</v>
+      </c>
+      <c r="N19">
+        <v>22</v>
+      </c>
+      <c r="O19">
+        <v>22</v>
+      </c>
+      <c r="P19">
+        <v>30</v>
+      </c>
+      <c r="Q19">
+        <v>53</v>
+      </c>
+      <c r="R19">
+        <v>43</v>
+      </c>
+      <c r="S19">
+        <v>45</v>
+      </c>
+      <c r="T19">
+        <v>41</v>
+      </c>
+      <c r="U19">
+        <v>44</v>
+      </c>
+      <c r="V19">
+        <v>36</v>
+      </c>
+      <c r="W19">
+        <v>55</v>
+      </c>
+      <c r="X19">
+        <v>68</v>
+      </c>
+      <c r="Y19">
+        <v>70</v>
+      </c>
+      <c r="Z19">
+        <v>70</v>
+      </c>
+      <c r="AA19">
+        <v>60</v>
+      </c>
+      <c r="AB19">
+        <v>45</v>
+      </c>
+      <c r="AC19">
+        <v>31</v>
+      </c>
+      <c r="AD19">
+        <v>28</v>
+      </c>
+      <c r="AE19">
+        <v>32</v>
+      </c>
+      <c r="AF19">
+        <v>20</v>
+      </c>
+      <c r="AG19">
+        <v>17</v>
+      </c>
+      <c r="AH19">
+        <v>5</v>
+      </c>
+      <c r="AI19">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>4</v>
+      </c>
+      <c r="AK19">
+        <v>5</v>
+      </c>
+      <c r="AL19">
+        <v>1</v>
+      </c>
+      <c r="AM19">
+        <v>2</v>
+      </c>
+      <c r="AN19">
+        <v>7</v>
+      </c>
+      <c r="AO19">
+        <v>7</v>
+      </c>
+      <c r="AP19">
         <v>10</v>
       </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
+      <c r="AQ19">
+        <v>15</v>
+      </c>
+      <c r="AR19">
+        <v>13</v>
+      </c>
+      <c r="AS19">
+        <v>20</v>
+      </c>
+      <c r="AT19">
+        <v>43</v>
+      </c>
+      <c r="AU19">
+        <v>41</v>
+      </c>
+      <c r="AV19">
+        <v>38</v>
+      </c>
+      <c r="AW19">
+        <v>34</v>
+      </c>
+      <c r="AX19">
+        <v>37</v>
+      </c>
+      <c r="AY19">
+        <v>14</v>
+      </c>
+      <c r="AZ19">
+        <v>23</v>
+      </c>
+      <c r="BA19">
         <v>7</v>
       </c>
-      <c r="K19">
-        <v>16</v>
-      </c>
-      <c r="L19">
-        <v>22</v>
-      </c>
-      <c r="M19">
-        <v>24</v>
-      </c>
-      <c r="N19">
-        <v>44</v>
-      </c>
-      <c r="O19">
-        <v>40</v>
-      </c>
-      <c r="P19">
-        <v>64</v>
-      </c>
-      <c r="Q19">
-        <v>90</v>
-      </c>
-      <c r="R19">
-        <v>85</v>
-      </c>
-      <c r="S19">
-        <v>90</v>
-      </c>
-      <c r="T19">
-        <v>86</v>
-      </c>
-      <c r="U19">
-        <v>87</v>
-      </c>
-      <c r="V19">
-        <v>119</v>
-      </c>
-      <c r="W19">
-        <v>133</v>
-      </c>
-      <c r="X19">
-        <v>185</v>
-      </c>
-      <c r="Y19">
-        <v>196</v>
-      </c>
-      <c r="Z19">
-        <v>197</v>
-      </c>
-      <c r="AA19">
-        <v>152</v>
-      </c>
-      <c r="AB19">
-        <v>119</v>
-      </c>
-      <c r="AC19">
-        <v>88</v>
-      </c>
-      <c r="AD19">
-        <v>64</v>
-      </c>
-      <c r="AE19">
-        <v>50</v>
-      </c>
-      <c r="AF19">
-        <v>43</v>
-      </c>
-      <c r="AG19">
-        <v>52</v>
-      </c>
-      <c r="AH19">
-        <v>32</v>
-      </c>
-      <c r="AI19">
-        <v>32</v>
-      </c>
-      <c r="AJ19">
-        <v>31</v>
-      </c>
-      <c r="AK19">
-        <v>50</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
+      <c r="BB19">
+        <v>11</v>
+      </c>
+      <c r="BC19">
         <v>4</v>
       </c>
-      <c r="AN19">
+      <c r="BD19">
+        <v>3</v>
+      </c>
+      <c r="BE19">
         <v>4</v>
       </c>
-      <c r="AO19">
-        <v>9</v>
-      </c>
-      <c r="AP19">
-        <v>18</v>
-      </c>
-      <c r="AQ19">
-        <v>31</v>
-      </c>
-      <c r="AR19">
-        <v>22</v>
-      </c>
-      <c r="AS19">
-        <v>30</v>
-      </c>
-      <c r="AT19">
-        <v>30</v>
-      </c>
-      <c r="AU19">
-        <v>33</v>
-      </c>
-      <c r="AV19">
-        <v>34</v>
-      </c>
-      <c r="AW19">
-        <v>31</v>
-      </c>
-      <c r="AX19">
-        <v>41</v>
-      </c>
-      <c r="AY19">
-        <v>51</v>
-      </c>
-      <c r="AZ19">
-        <v>37</v>
-      </c>
-      <c r="BA19">
-        <v>23</v>
-      </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
-      <c r="BC19">
-        <v>5</v>
-      </c>
-      <c r="BD19">
-        <v>1</v>
-      </c>
-      <c r="BE19">
-        <v>1</v>
-      </c>
       <c r="BF19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BG19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH19">
         <v>0</v>
       </c>
       <c r="BI19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL19">
         <v>0</v>
       </c>
       <c r="BM19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BN19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:66" x14ac:dyDescent="0.3">
@@ -62592,187 +62612,187 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
+        <v>7</v>
+      </c>
+      <c r="K20">
+        <v>16</v>
+      </c>
+      <c r="L20">
+        <v>22</v>
+      </c>
+      <c r="M20">
+        <v>24</v>
+      </c>
+      <c r="N20">
+        <v>44</v>
+      </c>
+      <c r="O20">
+        <v>40</v>
+      </c>
+      <c r="P20">
+        <v>64</v>
+      </c>
+      <c r="Q20">
+        <v>90</v>
+      </c>
+      <c r="R20">
+        <v>85</v>
+      </c>
+      <c r="S20">
+        <v>90</v>
+      </c>
+      <c r="T20">
+        <v>86</v>
+      </c>
+      <c r="U20">
+        <v>87</v>
+      </c>
+      <c r="V20">
+        <v>119</v>
+      </c>
+      <c r="W20">
+        <v>133</v>
+      </c>
+      <c r="X20">
+        <v>185</v>
+      </c>
+      <c r="Y20">
+        <v>196</v>
+      </c>
+      <c r="Z20">
+        <v>197</v>
+      </c>
+      <c r="AA20">
+        <v>152</v>
+      </c>
+      <c r="AB20">
+        <v>119</v>
+      </c>
+      <c r="AC20">
+        <v>88</v>
+      </c>
+      <c r="AD20">
+        <v>64</v>
+      </c>
+      <c r="AE20">
+        <v>50</v>
+      </c>
+      <c r="AF20">
+        <v>43</v>
+      </c>
+      <c r="AG20">
+        <v>52</v>
+      </c>
+      <c r="AH20">
+        <v>32</v>
+      </c>
+      <c r="AI20">
+        <v>32</v>
+      </c>
+      <c r="AJ20">
+        <v>31</v>
+      </c>
+      <c r="AK20">
+        <v>50</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>4</v>
+      </c>
+      <c r="AN20">
+        <v>4</v>
+      </c>
+      <c r="AO20">
+        <v>9</v>
+      </c>
+      <c r="AP20">
+        <v>18</v>
+      </c>
+      <c r="AQ20">
+        <v>31</v>
+      </c>
+      <c r="AR20">
+        <v>22</v>
+      </c>
+      <c r="AS20">
+        <v>30</v>
+      </c>
+      <c r="AT20">
+        <v>30</v>
+      </c>
+      <c r="AU20">
+        <v>33</v>
+      </c>
+      <c r="AV20">
+        <v>34</v>
+      </c>
+      <c r="AW20">
+        <v>31</v>
+      </c>
+      <c r="AX20">
+        <v>41</v>
+      </c>
+      <c r="AY20">
+        <v>51</v>
+      </c>
+      <c r="AZ20">
+        <v>37</v>
+      </c>
+      <c r="BA20">
+        <v>23</v>
+      </c>
+      <c r="BB20">
+        <v>1</v>
+      </c>
+      <c r="BC20">
+        <v>5</v>
+      </c>
+      <c r="BD20">
+        <v>1</v>
+      </c>
+      <c r="BE20">
+        <v>1</v>
+      </c>
+      <c r="BF20">
+        <v>7</v>
+      </c>
+      <c r="BG20">
+        <v>2</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>2</v>
+      </c>
+      <c r="BJ20">
         <v>3</v>
       </c>
-      <c r="K20">
+      <c r="BK20">
         <v>3</v>
       </c>
-      <c r="L20">
-        <v>3</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>4</v>
-      </c>
-      <c r="O20">
-        <v>12</v>
-      </c>
-      <c r="P20">
-        <v>17</v>
-      </c>
-      <c r="Q20">
-        <v>39</v>
-      </c>
-      <c r="R20">
-        <v>38</v>
-      </c>
-      <c r="S20">
-        <v>33</v>
-      </c>
-      <c r="T20">
-        <v>40</v>
-      </c>
-      <c r="U20">
-        <v>38</v>
-      </c>
-      <c r="V20">
-        <v>52</v>
-      </c>
-      <c r="W20">
-        <v>84</v>
-      </c>
-      <c r="X20">
-        <v>112</v>
-      </c>
-      <c r="Y20">
-        <v>210</v>
-      </c>
-      <c r="Z20">
-        <v>340</v>
-      </c>
-      <c r="AA20">
-        <v>327</v>
-      </c>
-      <c r="AB20">
-        <v>246</v>
-      </c>
-      <c r="AC20">
-        <v>135</v>
-      </c>
-      <c r="AD20">
-        <v>88</v>
-      </c>
-      <c r="AE20">
-        <v>62</v>
-      </c>
-      <c r="AF20">
-        <v>62</v>
-      </c>
-      <c r="AG20">
-        <v>34</v>
-      </c>
-      <c r="AH20">
-        <v>14</v>
-      </c>
-      <c r="AI20">
-        <v>5</v>
-      </c>
-      <c r="AJ20">
-        <v>11</v>
-      </c>
-      <c r="AK20">
-        <v>29</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>2</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>6</v>
-      </c>
-      <c r="AP20">
-        <v>16</v>
-      </c>
-      <c r="AQ20">
-        <v>29</v>
-      </c>
-      <c r="AR20">
-        <v>42</v>
-      </c>
-      <c r="AS20">
-        <v>37</v>
-      </c>
-      <c r="AT20">
-        <v>20</v>
-      </c>
-      <c r="AU20">
-        <v>23</v>
-      </c>
-      <c r="AV20">
-        <v>37</v>
-      </c>
-      <c r="AW20">
-        <v>52</v>
-      </c>
-      <c r="AX20">
-        <v>65</v>
-      </c>
-      <c r="AY20">
-        <v>133</v>
-      </c>
-      <c r="AZ20">
-        <v>148</v>
-      </c>
-      <c r="BA20">
-        <v>132</v>
-      </c>
-      <c r="BB20">
-        <v>100</v>
-      </c>
-      <c r="BC20">
-        <v>46</v>
-      </c>
-      <c r="BD20">
-        <v>31</v>
-      </c>
-      <c r="BE20">
-        <v>14</v>
-      </c>
-      <c r="BF20">
-        <v>10</v>
-      </c>
-      <c r="BG20">
-        <v>7</v>
-      </c>
-      <c r="BH20">
-        <v>7</v>
-      </c>
-      <c r="BI20">
-        <v>1</v>
-      </c>
-      <c r="BJ20">
-        <v>0</v>
-      </c>
-      <c r="BK20">
-        <v>0</v>
-      </c>
       <c r="BL20">
         <v>0</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:66" x14ac:dyDescent="0.3">
@@ -62792,187 +62812,187 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>3</v>
       </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
       <c r="K21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O21">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P21">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Q21">
+        <v>39</v>
+      </c>
+      <c r="R21">
         <v>38</v>
       </c>
-      <c r="R21">
-        <v>47</v>
-      </c>
       <c r="S21">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="T21">
         <v>40</v>
       </c>
       <c r="U21">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="V21">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="W21">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="X21">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="Y21">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="Z21">
-        <v>194</v>
+        <v>340</v>
       </c>
       <c r="AA21">
-        <v>211</v>
+        <v>327</v>
       </c>
       <c r="AB21">
+        <v>246</v>
+      </c>
+      <c r="AC21">
+        <v>135</v>
+      </c>
+      <c r="AD21">
+        <v>88</v>
+      </c>
+      <c r="AE21">
+        <v>62</v>
+      </c>
+      <c r="AF21">
+        <v>62</v>
+      </c>
+      <c r="AG21">
+        <v>34</v>
+      </c>
+      <c r="AH21">
+        <v>14</v>
+      </c>
+      <c r="AI21">
+        <v>5</v>
+      </c>
+      <c r="AJ21">
+        <v>11</v>
+      </c>
+      <c r="AK21">
+        <v>29</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>2</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>6</v>
+      </c>
+      <c r="AP21">
+        <v>16</v>
+      </c>
+      <c r="AQ21">
+        <v>29</v>
+      </c>
+      <c r="AR21">
+        <v>42</v>
+      </c>
+      <c r="AS21">
+        <v>37</v>
+      </c>
+      <c r="AT21">
+        <v>20</v>
+      </c>
+      <c r="AU21">
+        <v>23</v>
+      </c>
+      <c r="AV21">
+        <v>37</v>
+      </c>
+      <c r="AW21">
+        <v>52</v>
+      </c>
+      <c r="AX21">
+        <v>65</v>
+      </c>
+      <c r="AY21">
         <v>133</v>
       </c>
-      <c r="AC21">
-        <v>78</v>
-      </c>
-      <c r="AD21">
+      <c r="AZ21">
+        <v>148</v>
+      </c>
+      <c r="BA21">
+        <v>132</v>
+      </c>
+      <c r="BB21">
+        <v>100</v>
+      </c>
+      <c r="BC21">
         <v>46</v>
       </c>
-      <c r="AE21">
-        <v>63</v>
-      </c>
-      <c r="AF21">
-        <v>53</v>
-      </c>
-      <c r="AG21">
-        <v>50</v>
-      </c>
-      <c r="AH21">
-        <v>44</v>
-      </c>
-      <c r="AI21">
-        <v>39</v>
-      </c>
-      <c r="AJ21">
-        <v>44</v>
-      </c>
-      <c r="AK21">
-        <v>41</v>
-      </c>
-      <c r="AL21">
+      <c r="BD21">
+        <v>31</v>
+      </c>
+      <c r="BE21">
+        <v>14</v>
+      </c>
+      <c r="BF21">
+        <v>10</v>
+      </c>
+      <c r="BG21">
         <v>7</v>
       </c>
-      <c r="AM21">
-        <v>2</v>
-      </c>
-      <c r="AN21">
-        <v>11</v>
-      </c>
-      <c r="AO21">
-        <v>14</v>
-      </c>
-      <c r="AP21">
-        <v>15</v>
-      </c>
-      <c r="AQ21">
-        <v>31</v>
-      </c>
-      <c r="AR21">
-        <v>24</v>
-      </c>
-      <c r="AS21">
-        <v>29</v>
-      </c>
-      <c r="AT21">
-        <v>44</v>
-      </c>
-      <c r="AU21">
-        <v>45</v>
-      </c>
-      <c r="AV21">
-        <v>57</v>
-      </c>
-      <c r="AW21">
-        <v>61</v>
-      </c>
-      <c r="AX21">
-        <v>96</v>
-      </c>
-      <c r="AY21">
-        <v>81</v>
-      </c>
-      <c r="AZ21">
-        <v>106</v>
-      </c>
-      <c r="BA21">
-        <v>51</v>
-      </c>
-      <c r="BB21">
-        <v>43</v>
-      </c>
-      <c r="BC21">
-        <v>41</v>
-      </c>
-      <c r="BD21">
-        <v>27</v>
-      </c>
-      <c r="BE21">
-        <v>32</v>
-      </c>
-      <c r="BF21">
-        <v>22</v>
-      </c>
-      <c r="BG21">
-        <v>27</v>
-      </c>
       <c r="BH21">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BI21">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="BJ21">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BK21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BL21">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BM21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BN21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:66" x14ac:dyDescent="0.3">
@@ -62992,187 +63012,187 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>6</v>
+      </c>
+      <c r="L22">
+        <v>15</v>
+      </c>
+      <c r="M22">
         <v>5</v>
       </c>
-      <c r="J22">
-        <v>5</v>
-      </c>
-      <c r="K22">
-        <v>11</v>
-      </c>
-      <c r="L22">
-        <v>32</v>
-      </c>
-      <c r="M22">
-        <v>57</v>
-      </c>
       <c r="N22">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="O22">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="P22">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="Q22">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="R22">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="S22">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="T22">
+        <v>40</v>
+      </c>
+      <c r="U22">
+        <v>43</v>
+      </c>
+      <c r="V22">
+        <v>41</v>
+      </c>
+      <c r="W22">
+        <v>54</v>
+      </c>
+      <c r="X22">
+        <v>99</v>
+      </c>
+      <c r="Y22">
+        <v>152</v>
+      </c>
+      <c r="Z22">
+        <v>194</v>
+      </c>
+      <c r="AA22">
+        <v>211</v>
+      </c>
+      <c r="AB22">
         <v>133</v>
       </c>
-      <c r="U22">
-        <v>174</v>
-      </c>
-      <c r="V22">
-        <v>170</v>
-      </c>
-      <c r="W22">
-        <v>179</v>
-      </c>
-      <c r="X22">
-        <v>273</v>
-      </c>
-      <c r="Y22">
-        <v>377</v>
-      </c>
-      <c r="Z22">
-        <v>476</v>
-      </c>
-      <c r="AA22">
-        <v>531</v>
-      </c>
-      <c r="AB22">
-        <v>366</v>
-      </c>
       <c r="AC22">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD22">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="AE22">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="AF22">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="AG22">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="AH22">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="AI22">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="AJ22">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AK22">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AL22">
         <v>7</v>
       </c>
       <c r="AM22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AN22">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AO22">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="AP22">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="AQ22">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="AR22">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="AS22">
+        <v>29</v>
+      </c>
+      <c r="AT22">
+        <v>44</v>
+      </c>
+      <c r="AU22">
+        <v>45</v>
+      </c>
+      <c r="AV22">
+        <v>57</v>
+      </c>
+      <c r="AW22">
+        <v>61</v>
+      </c>
+      <c r="AX22">
         <v>96</v>
       </c>
-      <c r="AT22">
-        <v>118</v>
-      </c>
-      <c r="AU22">
-        <v>115</v>
-      </c>
-      <c r="AV22">
-        <v>152</v>
-      </c>
-      <c r="AW22">
-        <v>169</v>
-      </c>
-      <c r="AX22">
-        <v>183</v>
-      </c>
       <c r="AY22">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AZ22">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="BA22">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="BB22">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="BC22">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BD22">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="BE22">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="BF22">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BG22">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH22">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BI22">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BJ22">
+        <v>21</v>
+      </c>
+      <c r="BK22">
+        <v>20</v>
+      </c>
+      <c r="BL22">
         <v>15</v>
       </c>
-      <c r="BK22">
-        <v>10</v>
-      </c>
-      <c r="BL22">
-        <v>14</v>
-      </c>
       <c r="BM22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN22">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:66" x14ac:dyDescent="0.3">
@@ -63192,7 +63212,7 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -63201,178 +63221,178 @@
         <v>200</v>
       </c>
       <c r="I23">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="L23">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M23">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N23">
+        <v>66</v>
+      </c>
+      <c r="O23">
+        <v>67</v>
+      </c>
+      <c r="P23">
         <v>82</v>
       </c>
-      <c r="O23">
-        <v>102</v>
-      </c>
-      <c r="P23">
-        <v>145</v>
-      </c>
       <c r="Q23">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="R23">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="S23">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="T23">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="U23">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="V23">
-        <v>269</v>
+        <v>170</v>
       </c>
       <c r="W23">
-        <v>246</v>
+        <v>179</v>
       </c>
       <c r="X23">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="Y23">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="Z23">
-        <v>279</v>
+        <v>476</v>
       </c>
       <c r="AA23">
-        <v>304</v>
+        <v>531</v>
       </c>
       <c r="AB23">
-        <v>223</v>
+        <v>366</v>
       </c>
       <c r="AC23">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="AD23">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="AE23">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="AF23">
         <v>101</v>
       </c>
       <c r="AG23">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AH23">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI23">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AJ23">
+        <v>40</v>
+      </c>
+      <c r="AK23">
         <v>35</v>
       </c>
-      <c r="AK23">
-        <v>50</v>
-      </c>
       <c r="AL23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM23">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AN23">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AO23">
         <v>46</v>
       </c>
       <c r="AP23">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="AQ23">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AR23">
         <v>105</v>
       </c>
       <c r="AS23">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="AT23">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="AU23">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="AV23">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="AW23">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="AX23">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="AY23">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AZ23">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="BA23">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="BB23">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="BC23">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="BD23">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="BE23">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="BF23">
+        <v>32</v>
+      </c>
+      <c r="BG23">
+        <v>28</v>
+      </c>
+      <c r="BH23">
+        <v>22</v>
+      </c>
+      <c r="BI23">
+        <v>19</v>
+      </c>
+      <c r="BJ23">
+        <v>15</v>
+      </c>
+      <c r="BK23">
+        <v>10</v>
+      </c>
+      <c r="BL23">
         <v>14</v>
       </c>
-      <c r="BG23">
-        <v>11</v>
-      </c>
-      <c r="BH23">
-        <v>8</v>
-      </c>
-      <c r="BI23">
-        <v>12</v>
-      </c>
-      <c r="BJ23">
-        <v>12</v>
-      </c>
-      <c r="BK23">
-        <v>8</v>
-      </c>
-      <c r="BL23">
+      <c r="BM23">
+        <v>2</v>
+      </c>
+      <c r="BN23">
         <v>3</v>
-      </c>
-      <c r="BM23">
-        <v>4</v>
-      </c>
-      <c r="BN23">
-        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:66" x14ac:dyDescent="0.3">
@@ -63392,7 +63412,7 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -63401,178 +63421,178 @@
         <v>200</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J24">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K24">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L24">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M24">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="N24">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O24">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="P24">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="Q24">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="R24">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="S24">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="T24">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="U24">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="V24">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="W24">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="X24">
-        <v>500</v>
+        <v>246</v>
       </c>
       <c r="Y24">
-        <v>544</v>
+        <v>319</v>
       </c>
       <c r="Z24">
-        <v>670</v>
+        <v>279</v>
       </c>
       <c r="AA24">
-        <v>625</v>
+        <v>304</v>
       </c>
       <c r="AB24">
-        <v>471</v>
+        <v>223</v>
       </c>
       <c r="AC24">
-        <v>278</v>
+        <v>165</v>
       </c>
       <c r="AD24">
-        <v>164</v>
+        <v>99</v>
       </c>
       <c r="AE24">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="AF24">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AG24">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="AH24">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI24">
         <v>58</v>
       </c>
       <c r="AJ24">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AK24">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AL24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AM24">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AN24">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AO24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP24">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AQ24">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AR24">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="AS24">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="AT24">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="AU24">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AV24">
         <v>200</v>
       </c>
       <c r="AW24">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="AX24">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="AY24">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="AZ24">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="BA24">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="BB24">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="BC24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BD24">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="BE24">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BF24">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="BG24">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BH24">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BI24">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BJ24">
+        <v>12</v>
+      </c>
+      <c r="BK24">
         <v>8</v>
-      </c>
-      <c r="BK24">
-        <v>1</v>
       </c>
       <c r="BL24">
         <v>3</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN24">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:66" x14ac:dyDescent="0.3">
@@ -63592,7 +63612,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -63601,175 +63621,175 @@
         <v>200</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K25">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L25">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M25">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="N25">
-        <v>257</v>
+        <v>86</v>
       </c>
       <c r="O25">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="P25">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="Q25">
-        <v>435</v>
+        <v>121</v>
       </c>
       <c r="R25">
-        <v>466</v>
+        <v>137</v>
       </c>
       <c r="S25">
-        <v>497</v>
+        <v>166</v>
       </c>
       <c r="T25">
-        <v>459</v>
+        <v>216</v>
       </c>
       <c r="U25">
-        <v>452</v>
+        <v>230</v>
       </c>
       <c r="V25">
-        <v>528</v>
+        <v>233</v>
       </c>
       <c r="W25">
-        <v>579</v>
+        <v>311</v>
       </c>
       <c r="X25">
-        <v>643</v>
+        <v>500</v>
       </c>
       <c r="Y25">
-        <v>767</v>
+        <v>544</v>
       </c>
       <c r="Z25">
-        <v>888</v>
+        <v>670</v>
       </c>
       <c r="AA25">
-        <v>756</v>
+        <v>625</v>
       </c>
       <c r="AB25">
-        <v>565</v>
+        <v>471</v>
       </c>
       <c r="AC25">
-        <v>361</v>
+        <v>278</v>
       </c>
       <c r="AD25">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="AE25">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="AF25">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="AG25">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="AH25">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AI25">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="AJ25">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="AK25">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AL25">
+        <v>1</v>
+      </c>
+      <c r="AM25">
         <v>8</v>
       </c>
-      <c r="AM25">
-        <v>12</v>
-      </c>
       <c r="AN25">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AO25">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AP25">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AQ25">
+        <v>94</v>
+      </c>
+      <c r="AR25">
+        <v>128</v>
+      </c>
+      <c r="AS25">
+        <v>109</v>
+      </c>
+      <c r="AT25">
+        <v>143</v>
+      </c>
+      <c r="AU25">
+        <v>179</v>
+      </c>
+      <c r="AV25">
+        <v>200</v>
+      </c>
+      <c r="AW25">
         <v>239</v>
       </c>
-      <c r="AR25">
-        <v>294</v>
-      </c>
-      <c r="AS25">
-        <v>375</v>
-      </c>
-      <c r="AT25">
-        <v>430</v>
-      </c>
-      <c r="AU25">
-        <v>469</v>
-      </c>
-      <c r="AV25">
-        <v>423</v>
-      </c>
-      <c r="AW25">
-        <v>520</v>
-      </c>
       <c r="AX25">
-        <v>548</v>
+        <v>258</v>
       </c>
       <c r="AY25">
-        <v>545</v>
+        <v>238</v>
       </c>
       <c r="AZ25">
-        <v>424</v>
+        <v>235</v>
       </c>
       <c r="BA25">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="BB25">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="BC25">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="BD25">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="BE25">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="BF25">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="BG25">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH25">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BI25">
         <v>9</v>
       </c>
       <c r="BJ25">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BK25">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BL25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BM25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BN25">
         <v>6</v>
@@ -63792,7 +63812,7 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -63801,178 +63821,178 @@
         <v>200</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J26">
+        <v>20</v>
+      </c>
+      <c r="K26">
+        <v>19</v>
+      </c>
+      <c r="L26">
+        <v>66</v>
+      </c>
+      <c r="M26">
+        <v>139</v>
+      </c>
+      <c r="N26">
+        <v>257</v>
+      </c>
+      <c r="O26">
+        <v>346</v>
+      </c>
+      <c r="P26">
+        <v>413</v>
+      </c>
+      <c r="Q26">
+        <v>435</v>
+      </c>
+      <c r="R26">
+        <v>466</v>
+      </c>
+      <c r="S26">
+        <v>497</v>
+      </c>
+      <c r="T26">
+        <v>459</v>
+      </c>
+      <c r="U26">
+        <v>452</v>
+      </c>
+      <c r="V26">
+        <v>528</v>
+      </c>
+      <c r="W26">
+        <v>579</v>
+      </c>
+      <c r="X26">
+        <v>643</v>
+      </c>
+      <c r="Y26">
+        <v>767</v>
+      </c>
+      <c r="Z26">
+        <v>888</v>
+      </c>
+      <c r="AA26">
+        <v>756</v>
+      </c>
+      <c r="AB26">
+        <v>565</v>
+      </c>
+      <c r="AC26">
+        <v>361</v>
+      </c>
+      <c r="AD26">
+        <v>276</v>
+      </c>
+      <c r="AE26">
+        <v>169</v>
+      </c>
+      <c r="AF26">
+        <v>135</v>
+      </c>
+      <c r="AG26">
+        <v>116</v>
+      </c>
+      <c r="AH26">
+        <v>110</v>
+      </c>
+      <c r="AI26">
+        <v>102</v>
+      </c>
+      <c r="AJ26">
+        <v>87</v>
+      </c>
+      <c r="AK26">
+        <v>108</v>
+      </c>
+      <c r="AL26">
+        <v>8</v>
+      </c>
+      <c r="AM26">
+        <v>12</v>
+      </c>
+      <c r="AN26">
+        <v>26</v>
+      </c>
+      <c r="AO26">
+        <v>75</v>
+      </c>
+      <c r="AP26">
+        <v>116</v>
+      </c>
+      <c r="AQ26">
+        <v>239</v>
+      </c>
+      <c r="AR26">
+        <v>294</v>
+      </c>
+      <c r="AS26">
+        <v>375</v>
+      </c>
+      <c r="AT26">
+        <v>430</v>
+      </c>
+      <c r="AU26">
+        <v>469</v>
+      </c>
+      <c r="AV26">
+        <v>423</v>
+      </c>
+      <c r="AW26">
+        <v>520</v>
+      </c>
+      <c r="AX26">
+        <v>548</v>
+      </c>
+      <c r="AY26">
+        <v>545</v>
+      </c>
+      <c r="AZ26">
+        <v>424</v>
+      </c>
+      <c r="BA26">
+        <v>277</v>
+      </c>
+      <c r="BB26">
+        <v>154</v>
+      </c>
+      <c r="BC26">
+        <v>105</v>
+      </c>
+      <c r="BD26">
+        <v>74</v>
+      </c>
+      <c r="BE26">
+        <v>47</v>
+      </c>
+      <c r="BF26">
+        <v>41</v>
+      </c>
+      <c r="BG26">
+        <v>21</v>
+      </c>
+      <c r="BH26">
+        <v>7</v>
+      </c>
+      <c r="BI26">
+        <v>9</v>
+      </c>
+      <c r="BJ26">
+        <v>4</v>
+      </c>
+      <c r="BK26">
+        <v>9</v>
+      </c>
+      <c r="BL26">
+        <v>7</v>
+      </c>
+      <c r="BM26">
+        <v>4</v>
+      </c>
+      <c r="BN26">
         <v>6</v>
-      </c>
-      <c r="K26">
-        <v>12</v>
-      </c>
-      <c r="L26">
-        <v>25</v>
-      </c>
-      <c r="M26">
-        <v>40</v>
-      </c>
-      <c r="N26">
-        <v>89</v>
-      </c>
-      <c r="O26">
-        <v>104</v>
-      </c>
-      <c r="P26">
-        <v>117</v>
-      </c>
-      <c r="Q26">
-        <v>176</v>
-      </c>
-      <c r="R26">
-        <v>230</v>
-      </c>
-      <c r="S26">
-        <v>229</v>
-      </c>
-      <c r="T26">
-        <v>237</v>
-      </c>
-      <c r="U26">
-        <v>211</v>
-      </c>
-      <c r="V26">
-        <v>166</v>
-      </c>
-      <c r="W26">
-        <v>181</v>
-      </c>
-      <c r="X26">
-        <v>213</v>
-      </c>
-      <c r="Y26">
-        <v>222</v>
-      </c>
-      <c r="Z26">
-        <v>252</v>
-      </c>
-      <c r="AA26">
-        <v>232</v>
-      </c>
-      <c r="AB26">
-        <v>206</v>
-      </c>
-      <c r="AC26">
-        <v>133</v>
-      </c>
-      <c r="AD26">
-        <v>100</v>
-      </c>
-      <c r="AE26">
-        <v>57</v>
-      </c>
-      <c r="AF26">
-        <v>36</v>
-      </c>
-      <c r="AG26">
-        <v>34</v>
-      </c>
-      <c r="AH26">
-        <v>22</v>
-      </c>
-      <c r="AI26">
-        <v>19</v>
-      </c>
-      <c r="AJ26">
-        <v>18</v>
-      </c>
-      <c r="AK26">
-        <v>18</v>
-      </c>
-      <c r="AL26">
-        <v>3</v>
-      </c>
-      <c r="AM26">
-        <v>6</v>
-      </c>
-      <c r="AN26">
-        <v>11</v>
-      </c>
-      <c r="AO26">
-        <v>29</v>
-      </c>
-      <c r="AP26">
-        <v>23</v>
-      </c>
-      <c r="AQ26">
-        <v>55</v>
-      </c>
-      <c r="AR26">
-        <v>84</v>
-      </c>
-      <c r="AS26">
-        <v>126</v>
-      </c>
-      <c r="AT26">
-        <v>149</v>
-      </c>
-      <c r="AU26">
-        <v>201</v>
-      </c>
-      <c r="AV26">
-        <v>216</v>
-      </c>
-      <c r="AW26">
-        <v>141</v>
-      </c>
-      <c r="AX26">
-        <v>102</v>
-      </c>
-      <c r="AY26">
-        <v>114</v>
-      </c>
-      <c r="AZ26">
-        <v>88</v>
-      </c>
-      <c r="BA26">
-        <v>83</v>
-      </c>
-      <c r="BB26">
-        <v>37</v>
-      </c>
-      <c r="BC26">
-        <v>34</v>
-      </c>
-      <c r="BD26">
-        <v>21</v>
-      </c>
-      <c r="BE26">
-        <v>10</v>
-      </c>
-      <c r="BF26">
-        <v>14</v>
-      </c>
-      <c r="BG26">
-        <v>9</v>
-      </c>
-      <c r="BH26">
-        <v>3</v>
-      </c>
-      <c r="BI26">
-        <v>5</v>
-      </c>
-      <c r="BJ26">
-        <v>1</v>
-      </c>
-      <c r="BK26">
-        <v>3</v>
-      </c>
-      <c r="BL26">
-        <v>1</v>
-      </c>
-      <c r="BM26">
-        <v>1</v>
-      </c>
-      <c r="BN26">
-        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:66" x14ac:dyDescent="0.3">
@@ -63992,7 +64012,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -64001,178 +64021,178 @@
         <v>200</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L27">
         <v>25</v>
       </c>
       <c r="M27">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N27">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="O27">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="P27">
-        <v>214</v>
+        <v>117</v>
       </c>
       <c r="Q27">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="R27">
-        <v>344</v>
+        <v>230</v>
       </c>
       <c r="S27">
-        <v>380</v>
+        <v>229</v>
       </c>
       <c r="T27">
-        <v>400</v>
+        <v>237</v>
       </c>
       <c r="U27">
-        <v>396</v>
+        <v>211</v>
       </c>
       <c r="V27">
-        <v>364</v>
+        <v>166</v>
       </c>
       <c r="W27">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="X27">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="Y27">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="Z27">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="AA27">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="AB27">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="AC27">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="AD27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AE27">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AF27">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AG27">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AH27">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AI27">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ27">
         <v>18</v>
       </c>
       <c r="AK27">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN27">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO27">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AP27">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="AQ27">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AR27">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AS27">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="AT27">
-        <v>271</v>
+        <v>149</v>
       </c>
       <c r="AU27">
-        <v>259</v>
+        <v>201</v>
       </c>
       <c r="AV27">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="AW27">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c r="AX27">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="AY27">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="AZ27">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="BA27">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="BB27">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BC27">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BD27">
         <v>21</v>
       </c>
       <c r="BE27">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BF27">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG27">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BH27">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BI27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK27">
         <v>3</v>
       </c>
       <c r="BL27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM27">
         <v>1</v>
       </c>
       <c r="BN27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:66" x14ac:dyDescent="0.3">
@@ -64192,7 +64212,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -64201,175 +64221,175 @@
         <v>200</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K28">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L28">
+        <v>25</v>
+      </c>
+      <c r="M28">
+        <v>50</v>
+      </c>
+      <c r="N28">
+        <v>107</v>
+      </c>
+      <c r="O28">
+        <v>148</v>
+      </c>
+      <c r="P28">
+        <v>214</v>
+      </c>
+      <c r="Q28">
+        <v>286</v>
+      </c>
+      <c r="R28">
+        <v>344</v>
+      </c>
+      <c r="S28">
+        <v>380</v>
+      </c>
+      <c r="T28">
+        <v>400</v>
+      </c>
+      <c r="U28">
+        <v>396</v>
+      </c>
+      <c r="V28">
+        <v>364</v>
+      </c>
+      <c r="W28">
+        <v>298</v>
+      </c>
+      <c r="X28">
+        <v>289</v>
+      </c>
+      <c r="Y28">
+        <v>283</v>
+      </c>
+      <c r="Z28">
+        <v>294</v>
+      </c>
+      <c r="AA28">
+        <v>254</v>
+      </c>
+      <c r="AB28">
+        <v>191</v>
+      </c>
+      <c r="AC28">
+        <v>172</v>
+      </c>
+      <c r="AD28">
+        <v>110</v>
+      </c>
+      <c r="AE28">
+        <v>65</v>
+      </c>
+      <c r="AF28">
+        <v>55</v>
+      </c>
+      <c r="AG28">
+        <v>42</v>
+      </c>
+      <c r="AH28">
+        <v>33</v>
+      </c>
+      <c r="AI28">
+        <v>17</v>
+      </c>
+      <c r="AJ28">
+        <v>18</v>
+      </c>
+      <c r="AK28">
+        <v>38</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>4</v>
+      </c>
+      <c r="AN28">
+        <v>9</v>
+      </c>
+      <c r="AO28">
+        <v>24</v>
+      </c>
+      <c r="AP28">
         <v>45</v>
       </c>
-      <c r="M28">
-        <v>59</v>
-      </c>
-      <c r="N28">
-        <v>62</v>
-      </c>
-      <c r="O28">
+      <c r="AQ28">
         <v>80</v>
       </c>
-      <c r="P28">
-        <v>132</v>
-      </c>
-      <c r="Q28">
-        <v>143</v>
-      </c>
-      <c r="R28">
-        <v>218</v>
-      </c>
-      <c r="S28">
-        <v>264</v>
-      </c>
-      <c r="T28">
-        <v>342</v>
-      </c>
-      <c r="U28">
-        <v>393</v>
-      </c>
-      <c r="V28">
-        <v>522</v>
-      </c>
-      <c r="W28">
-        <v>596</v>
-      </c>
-      <c r="X28">
-        <v>539</v>
-      </c>
-      <c r="Y28">
-        <v>520</v>
-      </c>
-      <c r="Z28">
-        <v>449</v>
-      </c>
-      <c r="AA28">
-        <v>374</v>
-      </c>
-      <c r="AB28">
-        <v>286</v>
-      </c>
-      <c r="AC28">
-        <v>266</v>
-      </c>
-      <c r="AD28">
-        <v>124</v>
-      </c>
-      <c r="AE28">
-        <v>93</v>
-      </c>
-      <c r="AF28">
-        <v>76</v>
-      </c>
-      <c r="AG28">
-        <v>47</v>
-      </c>
-      <c r="AH28">
-        <v>49</v>
-      </c>
-      <c r="AI28">
-        <v>33</v>
-      </c>
-      <c r="AJ28">
-        <v>20</v>
-      </c>
-      <c r="AK28">
-        <v>59</v>
-      </c>
-      <c r="AL28">
-        <v>2</v>
-      </c>
-      <c r="AM28">
+      <c r="AR28">
+        <v>138</v>
+      </c>
+      <c r="AS28">
+        <v>176</v>
+      </c>
+      <c r="AT28">
+        <v>271</v>
+      </c>
+      <c r="AU28">
+        <v>259</v>
+      </c>
+      <c r="AV28">
+        <v>256</v>
+      </c>
+      <c r="AW28">
+        <v>230</v>
+      </c>
+      <c r="AX28">
+        <v>150</v>
+      </c>
+      <c r="AY28">
+        <v>166</v>
+      </c>
+      <c r="AZ28">
+        <v>131</v>
+      </c>
+      <c r="BA28">
+        <v>78</v>
+      </c>
+      <c r="BB28">
+        <v>36</v>
+      </c>
+      <c r="BC28">
+        <v>26</v>
+      </c>
+      <c r="BD28">
+        <v>21</v>
+      </c>
+      <c r="BE28">
         <v>17</v>
       </c>
-      <c r="AN28">
-        <v>20</v>
-      </c>
-      <c r="AO28">
-        <v>30</v>
-      </c>
-      <c r="AP28">
-        <v>46</v>
-      </c>
-      <c r="AQ28">
-        <v>78</v>
-      </c>
-      <c r="AR28">
-        <v>91</v>
-      </c>
-      <c r="AS28">
-        <v>149</v>
-      </c>
-      <c r="AT28">
-        <v>190</v>
-      </c>
-      <c r="AU28">
-        <v>266</v>
-      </c>
-      <c r="AV28">
-        <v>367</v>
-      </c>
-      <c r="AW28">
-        <v>357</v>
-      </c>
-      <c r="AX28">
-        <v>227</v>
-      </c>
-      <c r="AY28">
-        <v>179</v>
-      </c>
-      <c r="AZ28">
-        <v>152</v>
-      </c>
-      <c r="BA28">
-        <v>109</v>
-      </c>
-      <c r="BB28">
-        <v>67</v>
-      </c>
-      <c r="BC28">
-        <v>37</v>
-      </c>
-      <c r="BD28">
-        <v>43</v>
-      </c>
-      <c r="BE28">
-        <v>37</v>
-      </c>
       <c r="BF28">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="BG28">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BH28">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BI28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BJ28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK28">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN28">
         <v>2</v>
@@ -64392,7 +64412,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -64401,169 +64421,169 @@
         <v>200</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K29">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L29">
+        <v>45</v>
+      </c>
+      <c r="M29">
+        <v>59</v>
+      </c>
+      <c r="N29">
+        <v>62</v>
+      </c>
+      <c r="O29">
+        <v>80</v>
+      </c>
+      <c r="P29">
+        <v>132</v>
+      </c>
+      <c r="Q29">
+        <v>143</v>
+      </c>
+      <c r="R29">
+        <v>218</v>
+      </c>
+      <c r="S29">
+        <v>264</v>
+      </c>
+      <c r="T29">
+        <v>342</v>
+      </c>
+      <c r="U29">
+        <v>393</v>
+      </c>
+      <c r="V29">
+        <v>522</v>
+      </c>
+      <c r="W29">
+        <v>596</v>
+      </c>
+      <c r="X29">
+        <v>539</v>
+      </c>
+      <c r="Y29">
+        <v>520</v>
+      </c>
+      <c r="Z29">
+        <v>449</v>
+      </c>
+      <c r="AA29">
+        <v>374</v>
+      </c>
+      <c r="AB29">
+        <v>286</v>
+      </c>
+      <c r="AC29">
+        <v>266</v>
+      </c>
+      <c r="AD29">
+        <v>124</v>
+      </c>
+      <c r="AE29">
+        <v>93</v>
+      </c>
+      <c r="AF29">
+        <v>76</v>
+      </c>
+      <c r="AG29">
+        <v>47</v>
+      </c>
+      <c r="AH29">
+        <v>49</v>
+      </c>
+      <c r="AI29">
+        <v>33</v>
+      </c>
+      <c r="AJ29">
+        <v>20</v>
+      </c>
+      <c r="AK29">
+        <v>59</v>
+      </c>
+      <c r="AL29">
+        <v>2</v>
+      </c>
+      <c r="AM29">
+        <v>17</v>
+      </c>
+      <c r="AN29">
+        <v>20</v>
+      </c>
+      <c r="AO29">
+        <v>30</v>
+      </c>
+      <c r="AP29">
+        <v>46</v>
+      </c>
+      <c r="AQ29">
         <v>78</v>
       </c>
-      <c r="M29">
-        <v>139</v>
-      </c>
-      <c r="N29">
-        <v>271</v>
-      </c>
-      <c r="O29">
-        <v>242</v>
-      </c>
-      <c r="P29">
-        <v>243</v>
-      </c>
-      <c r="Q29">
-        <v>252</v>
-      </c>
-      <c r="R29">
-        <v>288</v>
-      </c>
-      <c r="S29">
-        <v>372</v>
-      </c>
-      <c r="T29">
-        <v>368</v>
-      </c>
-      <c r="U29">
-        <v>412</v>
-      </c>
-      <c r="V29">
-        <v>520</v>
-      </c>
-      <c r="W29">
-        <v>599</v>
-      </c>
-      <c r="X29">
-        <v>659</v>
-      </c>
-      <c r="Y29">
-        <v>554</v>
-      </c>
-      <c r="Z29">
-        <v>417</v>
-      </c>
-      <c r="AA29">
-        <v>284</v>
-      </c>
-      <c r="AB29">
-        <v>233</v>
-      </c>
-      <c r="AC29">
-        <v>177</v>
-      </c>
-      <c r="AD29">
-        <v>102</v>
-      </c>
-      <c r="AE29">
-        <v>73</v>
-      </c>
-      <c r="AF29">
-        <v>62</v>
-      </c>
-      <c r="AG29">
-        <v>31</v>
-      </c>
-      <c r="AH29">
-        <v>21</v>
-      </c>
-      <c r="AI29">
-        <v>16</v>
-      </c>
-      <c r="AJ29">
-        <v>15</v>
-      </c>
-      <c r="AK29">
-        <v>21</v>
-      </c>
-      <c r="AL29">
-        <v>8</v>
-      </c>
-      <c r="AM29">
-        <v>19</v>
-      </c>
-      <c r="AN29">
-        <v>30</v>
-      </c>
-      <c r="AO29">
-        <v>68</v>
-      </c>
-      <c r="AP29">
-        <v>154</v>
-      </c>
-      <c r="AQ29">
-        <v>241</v>
-      </c>
       <c r="AR29">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="AS29">
-        <v>228</v>
+        <v>149</v>
       </c>
       <c r="AT29">
-        <v>231</v>
+        <v>190</v>
       </c>
       <c r="AU29">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AV29">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AW29">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="AX29">
-        <v>351</v>
+        <v>227</v>
       </c>
       <c r="AY29">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="AZ29">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="BA29">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="BB29">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="BC29">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="BD29">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BE29">
+        <v>37</v>
+      </c>
+      <c r="BF29">
+        <v>51</v>
+      </c>
+      <c r="BG29">
         <v>17</v>
       </c>
-      <c r="BF29">
-        <v>11</v>
-      </c>
-      <c r="BG29">
-        <v>15</v>
-      </c>
       <c r="BH29">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BI29">
+        <v>6</v>
+      </c>
+      <c r="BJ29">
         <v>4</v>
       </c>
-      <c r="BJ29">
-        <v>2</v>
-      </c>
       <c r="BK29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL29">
         <v>0</v>
@@ -64572,7 +64592,7 @@
         <v>0</v>
       </c>
       <c r="BN29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:66" x14ac:dyDescent="0.3">
@@ -64592,7 +64612,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -64601,175 +64621,175 @@
         <v>200</v>
       </c>
       <c r="I30">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K30">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L30">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="M30">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="N30">
-        <v>103</v>
+        <v>271</v>
       </c>
       <c r="O30">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="P30">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="Q30">
-        <v>315</v>
+        <v>252</v>
       </c>
       <c r="R30">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="S30">
-        <v>222</v>
+        <v>372</v>
       </c>
       <c r="T30">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c r="U30">
-        <v>260</v>
+        <v>412</v>
       </c>
       <c r="V30">
-        <v>331</v>
+        <v>520</v>
       </c>
       <c r="W30">
-        <v>467</v>
+        <v>599</v>
       </c>
       <c r="X30">
-        <v>613</v>
+        <v>659</v>
       </c>
       <c r="Y30">
-        <v>687</v>
+        <v>554</v>
       </c>
       <c r="Z30">
-        <v>590</v>
+        <v>417</v>
       </c>
       <c r="AA30">
-        <v>405</v>
+        <v>284</v>
       </c>
       <c r="AB30">
-        <v>298</v>
+        <v>233</v>
       </c>
       <c r="AC30">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AD30">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="AE30">
+        <v>73</v>
+      </c>
+      <c r="AF30">
+        <v>62</v>
+      </c>
+      <c r="AG30">
+        <v>31</v>
+      </c>
+      <c r="AH30">
+        <v>21</v>
+      </c>
+      <c r="AI30">
+        <v>16</v>
+      </c>
+      <c r="AJ30">
+        <v>15</v>
+      </c>
+      <c r="AK30">
+        <v>21</v>
+      </c>
+      <c r="AL30">
+        <v>8</v>
+      </c>
+      <c r="AM30">
+        <v>19</v>
+      </c>
+      <c r="AN30">
+        <v>30</v>
+      </c>
+      <c r="AO30">
         <v>68</v>
       </c>
-      <c r="AF30">
-        <v>38</v>
-      </c>
-      <c r="AG30">
-        <v>25</v>
-      </c>
-      <c r="AH30">
-        <v>18</v>
-      </c>
-      <c r="AI30">
+      <c r="AP30">
+        <v>154</v>
+      </c>
+      <c r="AQ30">
+        <v>241</v>
+      </c>
+      <c r="AR30">
+        <v>220</v>
+      </c>
+      <c r="AS30">
+        <v>228</v>
+      </c>
+      <c r="AT30">
+        <v>231</v>
+      </c>
+      <c r="AU30">
+        <v>267</v>
+      </c>
+      <c r="AV30">
+        <v>369</v>
+      </c>
+      <c r="AW30">
+        <v>388</v>
+      </c>
+      <c r="AX30">
+        <v>351</v>
+      </c>
+      <c r="AY30">
+        <v>245</v>
+      </c>
+      <c r="AZ30">
+        <v>200</v>
+      </c>
+      <c r="BA30">
+        <v>193</v>
+      </c>
+      <c r="BB30">
+        <v>128</v>
+      </c>
+      <c r="BC30">
+        <v>54</v>
+      </c>
+      <c r="BD30">
+        <v>42</v>
+      </c>
+      <c r="BE30">
+        <v>17</v>
+      </c>
+      <c r="BF30">
+        <v>11</v>
+      </c>
+      <c r="BG30">
         <v>15</v>
       </c>
-      <c r="AJ30">
+      <c r="BH30">
         <v>8</v>
       </c>
-      <c r="AK30">
-        <v>22</v>
-      </c>
-      <c r="AL30">
-        <v>2</v>
-      </c>
-      <c r="AM30">
-        <v>18</v>
-      </c>
-      <c r="AN30">
-        <v>19</v>
-      </c>
-      <c r="AO30">
-        <v>72</v>
-      </c>
-      <c r="AP30">
-        <v>69</v>
-      </c>
-      <c r="AQ30">
-        <v>90</v>
-      </c>
-      <c r="AR30">
-        <v>190</v>
-      </c>
-      <c r="AS30">
-        <v>288</v>
-      </c>
-      <c r="AT30">
-        <v>270</v>
-      </c>
-      <c r="AU30">
-        <v>256</v>
-      </c>
-      <c r="AV30">
-        <v>257</v>
-      </c>
-      <c r="AW30">
-        <v>354</v>
-      </c>
-      <c r="AX30">
-        <v>353</v>
-      </c>
-      <c r="AY30">
-        <v>307</v>
-      </c>
-      <c r="AZ30">
-        <v>212</v>
-      </c>
-      <c r="BA30">
-        <v>222</v>
-      </c>
-      <c r="BB30">
-        <v>162</v>
-      </c>
-      <c r="BC30">
-        <v>112</v>
-      </c>
-      <c r="BD30">
-        <v>44</v>
-      </c>
-      <c r="BE30">
-        <v>38</v>
-      </c>
-      <c r="BF30">
-        <v>21</v>
-      </c>
-      <c r="BG30">
-        <v>9</v>
-      </c>
-      <c r="BH30">
-        <v>11</v>
-      </c>
       <c r="BI30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BL30">
         <v>0</v>
       </c>
       <c r="BM30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN30">
         <v>3</v>
@@ -64792,7 +64812,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -64801,178 +64821,178 @@
         <v>200</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K31">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L31">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M31">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="N31">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="O31">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="P31">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="Q31">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="R31">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="S31">
-        <v>348</v>
+        <v>222</v>
       </c>
       <c r="T31">
-        <v>332</v>
+        <v>229</v>
       </c>
       <c r="U31">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="V31">
+        <v>331</v>
+      </c>
+      <c r="W31">
+        <v>467</v>
+      </c>
+      <c r="X31">
+        <v>613</v>
+      </c>
+      <c r="Y31">
+        <v>687</v>
+      </c>
+      <c r="Z31">
+        <v>590</v>
+      </c>
+      <c r="AA31">
+        <v>405</v>
+      </c>
+      <c r="AB31">
+        <v>298</v>
+      </c>
+      <c r="AC31">
+        <v>179</v>
+      </c>
+      <c r="AD31">
+        <v>109</v>
+      </c>
+      <c r="AE31">
+        <v>68</v>
+      </c>
+      <c r="AF31">
+        <v>38</v>
+      </c>
+      <c r="AG31">
+        <v>25</v>
+      </c>
+      <c r="AH31">
+        <v>18</v>
+      </c>
+      <c r="AI31">
+        <v>15</v>
+      </c>
+      <c r="AJ31">
+        <v>8</v>
+      </c>
+      <c r="AK31">
+        <v>22</v>
+      </c>
+      <c r="AL31">
+        <v>2</v>
+      </c>
+      <c r="AM31">
+        <v>18</v>
+      </c>
+      <c r="AN31">
+        <v>19</v>
+      </c>
+      <c r="AO31">
+        <v>72</v>
+      </c>
+      <c r="AP31">
+        <v>69</v>
+      </c>
+      <c r="AQ31">
+        <v>90</v>
+      </c>
+      <c r="AR31">
+        <v>190</v>
+      </c>
+      <c r="AS31">
         <v>288</v>
       </c>
-      <c r="W31">
-        <v>378</v>
-      </c>
-      <c r="X31">
-        <v>441</v>
-      </c>
-      <c r="Y31">
-        <v>518</v>
-      </c>
-      <c r="Z31">
-        <v>434</v>
-      </c>
-      <c r="AA31">
-        <v>273</v>
-      </c>
-      <c r="AB31">
-        <v>175</v>
-      </c>
-      <c r="AC31">
-        <v>120</v>
-      </c>
-      <c r="AD31">
-        <v>52</v>
-      </c>
-      <c r="AE31">
-        <v>57</v>
-      </c>
-      <c r="AF31">
-        <v>33</v>
-      </c>
-      <c r="AG31">
-        <v>22</v>
-      </c>
-      <c r="AH31">
-        <v>23</v>
-      </c>
-      <c r="AI31">
-        <v>16</v>
-      </c>
-      <c r="AJ31">
-        <v>7</v>
-      </c>
-      <c r="AK31">
-        <v>18</v>
-      </c>
-      <c r="AL31">
-        <v>7</v>
-      </c>
-      <c r="AM31">
-        <v>7</v>
-      </c>
-      <c r="AN31">
-        <v>20</v>
-      </c>
-      <c r="AO31">
-        <v>41</v>
-      </c>
-      <c r="AP31">
-        <v>120</v>
-      </c>
-      <c r="AQ31">
-        <v>175</v>
-      </c>
-      <c r="AR31">
-        <v>239</v>
-      </c>
-      <c r="AS31">
-        <v>282</v>
-      </c>
       <c r="AT31">
-        <v>325</v>
+        <v>270</v>
       </c>
       <c r="AU31">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="AV31">
-        <v>325</v>
+        <v>257</v>
       </c>
       <c r="AW31">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="AX31">
+        <v>353</v>
+      </c>
+      <c r="AY31">
+        <v>307</v>
+      </c>
+      <c r="AZ31">
+        <v>212</v>
+      </c>
+      <c r="BA31">
         <v>222</v>
       </c>
-      <c r="AY31">
-        <v>208</v>
-      </c>
-      <c r="AZ31">
-        <v>138</v>
-      </c>
-      <c r="BA31">
-        <v>93</v>
-      </c>
       <c r="BB31">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="BC31">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="BD31">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="BE31">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BF31">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BG31">
         <v>9</v>
       </c>
       <c r="BH31">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BI31">
+        <v>2</v>
+      </c>
+      <c r="BJ31">
         <v>4</v>
       </c>
-      <c r="BJ31">
-        <v>2</v>
-      </c>
       <c r="BK31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BL31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BM31">
         <v>1</v>
       </c>
       <c r="BN31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:66" x14ac:dyDescent="0.3">
@@ -64992,7 +65012,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -65001,178 +65021,178 @@
         <v>200</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K32">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L32">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="M32">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="N32">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="O32">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="P32">
-        <v>181</v>
+        <v>310</v>
       </c>
       <c r="Q32">
-        <v>213</v>
+        <v>301</v>
       </c>
       <c r="R32">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="S32">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="T32">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="U32">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="V32">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="W32">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="X32">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="Y32">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="Z32">
-        <v>539</v>
+        <v>434</v>
       </c>
       <c r="AA32">
-        <v>358</v>
+        <v>273</v>
       </c>
       <c r="AB32">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="AC32">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="AD32">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="AE32">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AF32">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="AG32">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AH32">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI32">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AJ32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK32">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM32">
         <v>7</v>
       </c>
       <c r="AN32">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="AO32">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AP32">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="AQ32">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="AR32">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="AS32">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="AT32">
-        <v>209</v>
+        <v>325</v>
       </c>
       <c r="AU32">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="AV32">
-        <v>239</v>
+        <v>325</v>
       </c>
       <c r="AW32">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="AX32">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="AY32">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="AZ32">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="BA32">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="BB32">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="BC32">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="BD32">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BE32">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="BF32">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BG32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BH32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BI32">
         <v>4</v>
       </c>
       <c r="BJ32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BM32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:66" x14ac:dyDescent="0.3">
@@ -65192,7 +65212,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -65201,178 +65221,178 @@
         <v>200</v>
       </c>
       <c r="I33">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K33">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L33">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M33">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="N33">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="O33">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="P33">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q33">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="R33">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="S33">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="T33">
-        <v>422</v>
+        <v>301</v>
       </c>
       <c r="U33">
-        <v>468</v>
+        <v>313</v>
       </c>
       <c r="V33">
-        <v>486</v>
+        <v>336</v>
       </c>
       <c r="W33">
-        <v>510</v>
+        <v>388</v>
       </c>
       <c r="X33">
-        <v>524</v>
+        <v>458</v>
       </c>
       <c r="Y33">
-        <v>676</v>
+        <v>526</v>
       </c>
       <c r="Z33">
-        <v>590</v>
+        <v>539</v>
       </c>
       <c r="AA33">
-        <v>453</v>
+        <v>358</v>
       </c>
       <c r="AB33">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="AC33">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="AD33">
+        <v>105</v>
+      </c>
+      <c r="AE33">
+        <v>62</v>
+      </c>
+      <c r="AF33">
+        <v>54</v>
+      </c>
+      <c r="AG33">
+        <v>38</v>
+      </c>
+      <c r="AH33">
+        <v>25</v>
+      </c>
+      <c r="AI33">
+        <v>19</v>
+      </c>
+      <c r="AJ33">
+        <v>10</v>
+      </c>
+      <c r="AK33">
+        <v>16</v>
+      </c>
+      <c r="AL33">
+        <v>6</v>
+      </c>
+      <c r="AM33">
+        <v>7</v>
+      </c>
+      <c r="AN33">
+        <v>33</v>
+      </c>
+      <c r="AO33">
+        <v>43</v>
+      </c>
+      <c r="AP33">
+        <v>62</v>
+      </c>
+      <c r="AQ33">
+        <v>85</v>
+      </c>
+      <c r="AR33">
+        <v>148</v>
+      </c>
+      <c r="AS33">
+        <v>199</v>
+      </c>
+      <c r="AT33">
+        <v>209</v>
+      </c>
+      <c r="AU33">
+        <v>250</v>
+      </c>
+      <c r="AV33">
+        <v>239</v>
+      </c>
+      <c r="AW33">
+        <v>219</v>
+      </c>
+      <c r="AX33">
+        <v>194</v>
+      </c>
+      <c r="AY33">
+        <v>179</v>
+      </c>
+      <c r="AZ33">
         <v>142</v>
       </c>
-      <c r="AE33">
-        <v>105</v>
-      </c>
-      <c r="AF33">
-        <v>72</v>
-      </c>
-      <c r="AG33">
-        <v>52</v>
-      </c>
-      <c r="AH33">
-        <v>45</v>
-      </c>
-      <c r="AI33">
-        <v>26</v>
-      </c>
-      <c r="AJ33">
-        <v>22</v>
-      </c>
-      <c r="AK33">
-        <v>19</v>
-      </c>
-      <c r="AL33">
-        <v>12</v>
-      </c>
-      <c r="AM33">
-        <v>17</v>
-      </c>
-      <c r="AN33">
-        <v>16</v>
-      </c>
-      <c r="AO33">
-        <v>36</v>
-      </c>
-      <c r="AP33">
-        <v>113</v>
-      </c>
-      <c r="AQ33">
-        <v>121</v>
-      </c>
-      <c r="AR33">
-        <v>159</v>
-      </c>
-      <c r="AS33">
-        <v>237</v>
-      </c>
-      <c r="AT33">
-        <v>264</v>
-      </c>
-      <c r="AU33">
-        <v>429</v>
-      </c>
-      <c r="AV33">
-        <v>518</v>
-      </c>
-      <c r="AW33">
-        <v>569</v>
-      </c>
-      <c r="AX33">
-        <v>554</v>
-      </c>
-      <c r="AY33">
-        <v>471</v>
-      </c>
-      <c r="AZ33">
-        <v>346</v>
-      </c>
       <c r="BA33">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="BB33">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="BC33">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="BD33">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="BE33">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="BF33">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="BG33">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="BH33">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BI33">
+        <v>4</v>
+      </c>
+      <c r="BJ33">
         <v>3</v>
       </c>
-      <c r="BJ33">
-        <v>8</v>
-      </c>
       <c r="BK33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BN33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:66" x14ac:dyDescent="0.3">
@@ -65392,7 +65412,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -65401,175 +65421,175 @@
         <v>200</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K34">
+        <v>15</v>
+      </c>
+      <c r="L34">
+        <v>32</v>
+      </c>
+      <c r="M34">
+        <v>70</v>
+      </c>
+      <c r="N34">
+        <v>120</v>
+      </c>
+      <c r="O34">
+        <v>157</v>
+      </c>
+      <c r="P34">
+        <v>185</v>
+      </c>
+      <c r="Q34">
+        <v>229</v>
+      </c>
+      <c r="R34">
+        <v>253</v>
+      </c>
+      <c r="S34">
+        <v>355</v>
+      </c>
+      <c r="T34">
+        <v>422</v>
+      </c>
+      <c r="U34">
+        <v>468</v>
+      </c>
+      <c r="V34">
+        <v>486</v>
+      </c>
+      <c r="W34">
+        <v>510</v>
+      </c>
+      <c r="X34">
+        <v>524</v>
+      </c>
+      <c r="Y34">
+        <v>676</v>
+      </c>
+      <c r="Z34">
+        <v>590</v>
+      </c>
+      <c r="AA34">
+        <v>453</v>
+      </c>
+      <c r="AB34">
+        <v>262</v>
+      </c>
+      <c r="AC34">
+        <v>184</v>
+      </c>
+      <c r="AD34">
+        <v>142</v>
+      </c>
+      <c r="AE34">
+        <v>105</v>
+      </c>
+      <c r="AF34">
+        <v>72</v>
+      </c>
+      <c r="AG34">
+        <v>52</v>
+      </c>
+      <c r="AH34">
+        <v>45</v>
+      </c>
+      <c r="AI34">
+        <v>26</v>
+      </c>
+      <c r="AJ34">
+        <v>22</v>
+      </c>
+      <c r="AK34">
+        <v>19</v>
+      </c>
+      <c r="AL34">
+        <v>12</v>
+      </c>
+      <c r="AM34">
         <v>17</v>
       </c>
-      <c r="L34">
-        <v>46</v>
-      </c>
-      <c r="M34">
-        <v>72</v>
-      </c>
-      <c r="N34">
-        <v>122</v>
-      </c>
-      <c r="O34">
-        <v>142</v>
-      </c>
-      <c r="P34">
-        <v>198</v>
-      </c>
-      <c r="Q34">
-        <v>246</v>
-      </c>
-      <c r="R34">
-        <v>292</v>
-      </c>
-      <c r="S34">
-        <v>328</v>
-      </c>
-      <c r="T34">
-        <v>417</v>
-      </c>
-      <c r="U34">
-        <v>510</v>
-      </c>
-      <c r="V34">
-        <v>555</v>
-      </c>
-      <c r="W34">
-        <v>568</v>
-      </c>
-      <c r="X34">
-        <v>544</v>
-      </c>
-      <c r="Y34">
-        <v>552</v>
-      </c>
-      <c r="Z34">
-        <v>545</v>
-      </c>
-      <c r="AA34">
-        <v>433</v>
-      </c>
-      <c r="AB34">
-        <v>273</v>
-      </c>
-      <c r="AC34">
-        <v>135</v>
-      </c>
-      <c r="AD34">
-        <v>66</v>
-      </c>
-      <c r="AE34">
-        <v>33</v>
-      </c>
-      <c r="AF34">
-        <v>42</v>
-      </c>
-      <c r="AG34">
-        <v>28</v>
-      </c>
-      <c r="AH34">
-        <v>22</v>
-      </c>
-      <c r="AI34">
-        <v>12</v>
-      </c>
-      <c r="AJ34">
+      <c r="AN34">
         <v>16</v>
       </c>
-      <c r="AK34">
-        <v>10</v>
-      </c>
-      <c r="AL34">
+      <c r="AO34">
+        <v>36</v>
+      </c>
+      <c r="AP34">
+        <v>113</v>
+      </c>
+      <c r="AQ34">
+        <v>121</v>
+      </c>
+      <c r="AR34">
+        <v>159</v>
+      </c>
+      <c r="AS34">
+        <v>237</v>
+      </c>
+      <c r="AT34">
+        <v>264</v>
+      </c>
+      <c r="AU34">
+        <v>429</v>
+      </c>
+      <c r="AV34">
+        <v>518</v>
+      </c>
+      <c r="AW34">
+        <v>569</v>
+      </c>
+      <c r="AX34">
+        <v>554</v>
+      </c>
+      <c r="AY34">
+        <v>471</v>
+      </c>
+      <c r="AZ34">
+        <v>346</v>
+      </c>
+      <c r="BA34">
+        <v>256</v>
+      </c>
+      <c r="BB34">
+        <v>206</v>
+      </c>
+      <c r="BC34">
+        <v>161</v>
+      </c>
+      <c r="BD34">
+        <v>97</v>
+      </c>
+      <c r="BE34">
+        <v>62</v>
+      </c>
+      <c r="BF34">
+        <v>48</v>
+      </c>
+      <c r="BG34">
+        <v>51</v>
+      </c>
+      <c r="BH34">
+        <v>17</v>
+      </c>
+      <c r="BI34">
         <v>3</v>
       </c>
-      <c r="AM34">
-        <v>7</v>
-      </c>
-      <c r="AN34">
+      <c r="BJ34">
         <v>8</v>
       </c>
-      <c r="AO34">
-        <v>30</v>
-      </c>
-      <c r="AP34">
-        <v>53</v>
-      </c>
-      <c r="AQ34">
-        <v>95</v>
-      </c>
-      <c r="AR34">
-        <v>143</v>
-      </c>
-      <c r="AS34">
-        <v>197</v>
-      </c>
-      <c r="AT34">
-        <v>233</v>
-      </c>
-      <c r="AU34">
-        <v>252</v>
-      </c>
-      <c r="AV34">
-        <v>327</v>
-      </c>
-      <c r="AW34">
-        <v>341</v>
-      </c>
-      <c r="AX34">
-        <v>432</v>
-      </c>
-      <c r="AY34">
-        <v>392</v>
-      </c>
-      <c r="AZ34">
-        <v>282</v>
-      </c>
-      <c r="BA34">
-        <v>208</v>
-      </c>
-      <c r="BB34">
-        <v>104</v>
-      </c>
-      <c r="BC34">
-        <v>78</v>
-      </c>
-      <c r="BD34">
-        <v>55</v>
-      </c>
-      <c r="BE34">
-        <v>36</v>
-      </c>
-      <c r="BF34">
-        <v>20</v>
-      </c>
-      <c r="BG34">
-        <v>16</v>
-      </c>
-      <c r="BH34">
-        <v>10</v>
-      </c>
-      <c r="BI34">
-        <v>4</v>
-      </c>
-      <c r="BJ34">
-        <v>9</v>
-      </c>
       <c r="BK34">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BL34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN34">
         <v>2</v>
@@ -65592,7 +65612,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -65601,178 +65621,178 @@
         <v>200</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K35">
+        <v>17</v>
+      </c>
+      <c r="L35">
+        <v>46</v>
+      </c>
+      <c r="M35">
+        <v>72</v>
+      </c>
+      <c r="N35">
+        <v>122</v>
+      </c>
+      <c r="O35">
+        <v>142</v>
+      </c>
+      <c r="P35">
+        <v>198</v>
+      </c>
+      <c r="Q35">
+        <v>246</v>
+      </c>
+      <c r="R35">
+        <v>292</v>
+      </c>
+      <c r="S35">
+        <v>328</v>
+      </c>
+      <c r="T35">
+        <v>417</v>
+      </c>
+      <c r="U35">
+        <v>510</v>
+      </c>
+      <c r="V35">
+        <v>555</v>
+      </c>
+      <c r="W35">
+        <v>568</v>
+      </c>
+      <c r="X35">
+        <v>544</v>
+      </c>
+      <c r="Y35">
+        <v>552</v>
+      </c>
+      <c r="Z35">
+        <v>545</v>
+      </c>
+      <c r="AA35">
+        <v>433</v>
+      </c>
+      <c r="AB35">
+        <v>273</v>
+      </c>
+      <c r="AC35">
+        <v>135</v>
+      </c>
+      <c r="AD35">
+        <v>66</v>
+      </c>
+      <c r="AE35">
+        <v>33</v>
+      </c>
+      <c r="AF35">
+        <v>42</v>
+      </c>
+      <c r="AG35">
+        <v>28</v>
+      </c>
+      <c r="AH35">
+        <v>22</v>
+      </c>
+      <c r="AI35">
+        <v>12</v>
+      </c>
+      <c r="AJ35">
+        <v>16</v>
+      </c>
+      <c r="AK35">
         <v>10</v>
       </c>
-      <c r="L35">
-        <v>13</v>
-      </c>
-      <c r="M35">
-        <v>85</v>
-      </c>
-      <c r="N35">
-        <v>120</v>
-      </c>
-      <c r="O35">
-        <v>127</v>
-      </c>
-      <c r="P35">
-        <v>121</v>
-      </c>
-      <c r="Q35">
-        <v>192</v>
-      </c>
-      <c r="R35">
-        <v>239</v>
-      </c>
-      <c r="S35">
-        <v>214</v>
-      </c>
-      <c r="T35">
-        <v>298</v>
-      </c>
-      <c r="U35">
-        <v>331</v>
-      </c>
-      <c r="V35">
-        <v>454</v>
-      </c>
-      <c r="W35">
-        <v>612</v>
-      </c>
-      <c r="X35">
-        <v>554</v>
-      </c>
-      <c r="Y35">
-        <v>467</v>
-      </c>
-      <c r="Z35">
-        <v>412</v>
-      </c>
-      <c r="AA35">
-        <v>306</v>
-      </c>
-      <c r="AB35">
-        <v>211</v>
-      </c>
-      <c r="AC35">
-        <v>115</v>
-      </c>
-      <c r="AD35">
-        <v>59</v>
-      </c>
-      <c r="AE35">
-        <v>27</v>
-      </c>
-      <c r="AF35">
-        <v>22</v>
-      </c>
-      <c r="AG35">
+      <c r="AL35">
+        <v>3</v>
+      </c>
+      <c r="AM35">
+        <v>7</v>
+      </c>
+      <c r="AN35">
         <v>8</v>
       </c>
-      <c r="AH35">
-        <v>17</v>
-      </c>
-      <c r="AI35">
-        <v>4</v>
-      </c>
-      <c r="AJ35">
-        <v>6</v>
-      </c>
-      <c r="AK35">
-        <v>16</v>
-      </c>
-      <c r="AL35">
-        <v>6</v>
-      </c>
-      <c r="AM35">
-        <v>13</v>
-      </c>
-      <c r="AN35">
-        <v>11</v>
-      </c>
       <c r="AO35">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AP35">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="AQ35">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AR35">
         <v>143</v>
       </c>
       <c r="AS35">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="AT35">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="AU35">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="AV35">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="AW35">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="AX35">
-        <v>352</v>
+        <v>432</v>
       </c>
       <c r="AY35">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="AZ35">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="BA35">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="BB35">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="BC35">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="BD35">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BE35">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BF35">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BG35">
+        <v>16</v>
+      </c>
+      <c r="BH35">
         <v>10</v>
       </c>
-      <c r="BH35">
+      <c r="BI35">
         <v>4</v>
       </c>
-      <c r="BI35">
-        <v>2</v>
-      </c>
       <c r="BJ35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BK35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BN35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:66" x14ac:dyDescent="0.3">
@@ -65792,7 +65812,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -65801,178 +65821,178 @@
         <v>200</v>
       </c>
       <c r="I36">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K36">
+        <v>10</v>
+      </c>
+      <c r="L36">
+        <v>13</v>
+      </c>
+      <c r="M36">
+        <v>85</v>
+      </c>
+      <c r="N36">
+        <v>120</v>
+      </c>
+      <c r="O36">
+        <v>127</v>
+      </c>
+      <c r="P36">
+        <v>121</v>
+      </c>
+      <c r="Q36">
+        <v>192</v>
+      </c>
+      <c r="R36">
+        <v>239</v>
+      </c>
+      <c r="S36">
+        <v>214</v>
+      </c>
+      <c r="T36">
+        <v>298</v>
+      </c>
+      <c r="U36">
+        <v>331</v>
+      </c>
+      <c r="V36">
+        <v>454</v>
+      </c>
+      <c r="W36">
+        <v>612</v>
+      </c>
+      <c r="X36">
+        <v>554</v>
+      </c>
+      <c r="Y36">
+        <v>467</v>
+      </c>
+      <c r="Z36">
+        <v>412</v>
+      </c>
+      <c r="AA36">
+        <v>306</v>
+      </c>
+      <c r="AB36">
+        <v>211</v>
+      </c>
+      <c r="AC36">
+        <v>115</v>
+      </c>
+      <c r="AD36">
+        <v>59</v>
+      </c>
+      <c r="AE36">
+        <v>27</v>
+      </c>
+      <c r="AF36">
+        <v>22</v>
+      </c>
+      <c r="AG36">
+        <v>8</v>
+      </c>
+      <c r="AH36">
+        <v>17</v>
+      </c>
+      <c r="AI36">
+        <v>4</v>
+      </c>
+      <c r="AJ36">
+        <v>6</v>
+      </c>
+      <c r="AK36">
         <v>16</v>
       </c>
-      <c r="L36">
-        <v>37</v>
-      </c>
-      <c r="M36">
-        <v>62</v>
-      </c>
-      <c r="N36">
-        <v>113</v>
-      </c>
-      <c r="O36">
-        <v>141</v>
-      </c>
-      <c r="P36">
-        <v>126</v>
-      </c>
-      <c r="Q36">
-        <v>136</v>
-      </c>
-      <c r="R36">
-        <v>210</v>
-      </c>
-      <c r="S36">
-        <v>300</v>
-      </c>
-      <c r="T36">
-        <v>404</v>
-      </c>
-      <c r="U36">
-        <v>593</v>
-      </c>
-      <c r="V36">
-        <v>830</v>
-      </c>
-      <c r="W36">
-        <v>1008</v>
-      </c>
-      <c r="X36">
-        <v>1073</v>
-      </c>
-      <c r="Y36">
-        <v>1078</v>
-      </c>
-      <c r="Z36">
-        <v>993</v>
-      </c>
-      <c r="AA36">
-        <v>976</v>
-      </c>
-      <c r="AB36">
-        <v>881</v>
-      </c>
-      <c r="AC36">
-        <v>679</v>
-      </c>
-      <c r="AD36">
-        <v>531</v>
-      </c>
-      <c r="AE36">
+      <c r="AL36">
+        <v>6</v>
+      </c>
+      <c r="AM36">
+        <v>13</v>
+      </c>
+      <c r="AN36">
+        <v>11</v>
+      </c>
+      <c r="AO36">
+        <v>25</v>
+      </c>
+      <c r="AP36">
+        <v>125</v>
+      </c>
+      <c r="AQ36">
+        <v>140</v>
+      </c>
+      <c r="AR36">
+        <v>143</v>
+      </c>
+      <c r="AS36">
+        <v>155</v>
+      </c>
+      <c r="AT36">
+        <v>242</v>
+      </c>
+      <c r="AU36">
+        <v>238</v>
+      </c>
+      <c r="AV36">
+        <v>306</v>
+      </c>
+      <c r="AW36">
+        <v>329</v>
+      </c>
+      <c r="AX36">
+        <v>352</v>
+      </c>
+      <c r="AY36">
         <v>359</v>
       </c>
-      <c r="AF36">
-        <v>273</v>
-      </c>
-      <c r="AG36">
-        <v>188</v>
-      </c>
-      <c r="AH36">
-        <v>118</v>
-      </c>
-      <c r="AI36">
-        <v>100</v>
-      </c>
-      <c r="AJ36">
-        <v>72</v>
-      </c>
-      <c r="AK36">
-        <v>65</v>
-      </c>
-      <c r="AL36">
+      <c r="AZ36">
+        <v>291</v>
+      </c>
+      <c r="BA36">
+        <v>168</v>
+      </c>
+      <c r="BB36">
+        <v>87</v>
+      </c>
+      <c r="BC36">
+        <v>50</v>
+      </c>
+      <c r="BD36">
+        <v>29</v>
+      </c>
+      <c r="BE36">
         <v>24</v>
       </c>
-      <c r="AM36">
-        <v>41</v>
-      </c>
-      <c r="AN36">
-        <v>57</v>
-      </c>
-      <c r="AO36">
-        <v>80</v>
-      </c>
-      <c r="AP36">
-        <v>96</v>
-      </c>
-      <c r="AQ36">
-        <v>174</v>
-      </c>
-      <c r="AR36">
-        <v>193</v>
-      </c>
-      <c r="AS36">
-        <v>180</v>
-      </c>
-      <c r="AT36">
-        <v>251</v>
-      </c>
-      <c r="AU36">
-        <v>278</v>
-      </c>
-      <c r="AV36">
-        <v>292</v>
-      </c>
-      <c r="AW36">
-        <v>448</v>
-      </c>
-      <c r="AX36">
-        <v>518</v>
-      </c>
-      <c r="AY36">
-        <v>501</v>
-      </c>
-      <c r="AZ36">
-        <v>440</v>
-      </c>
-      <c r="BA36">
-        <v>328</v>
-      </c>
-      <c r="BB36">
-        <v>237</v>
-      </c>
-      <c r="BC36">
-        <v>185</v>
-      </c>
-      <c r="BD36">
-        <v>183</v>
-      </c>
-      <c r="BE36">
-        <v>106</v>
-      </c>
       <c r="BF36">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="BG36">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="BH36">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="BI36">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="BJ36">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="BK36">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BL36">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="BM36">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BN36">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:66" x14ac:dyDescent="0.3">
@@ -65992,7 +66012,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -66001,178 +66021,178 @@
         <v>200</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K37">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L37">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="M37">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="N37">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="O37">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P37">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="Q37">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="R37">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="S37">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="T37">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="U37">
-        <v>462</v>
+        <v>593</v>
       </c>
       <c r="V37">
-        <v>586</v>
+        <v>830</v>
       </c>
       <c r="W37">
-        <v>801</v>
+        <v>1008</v>
       </c>
       <c r="X37">
-        <v>985</v>
+        <v>1073</v>
       </c>
       <c r="Y37">
-        <v>972</v>
+        <v>1078</v>
       </c>
       <c r="Z37">
-        <v>876</v>
+        <v>993</v>
       </c>
       <c r="AA37">
-        <v>684</v>
+        <v>976</v>
       </c>
       <c r="AB37">
-        <v>488</v>
+        <v>881</v>
       </c>
       <c r="AC37">
-        <v>343</v>
+        <v>679</v>
       </c>
       <c r="AD37">
-        <v>245</v>
+        <v>531</v>
       </c>
       <c r="AE37">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="AF37">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AG37">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AH37">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="AI37">
+        <v>100</v>
+      </c>
+      <c r="AJ37">
+        <v>72</v>
+      </c>
+      <c r="AK37">
+        <v>65</v>
+      </c>
+      <c r="AL37">
+        <v>24</v>
+      </c>
+      <c r="AM37">
+        <v>41</v>
+      </c>
+      <c r="AN37">
+        <v>57</v>
+      </c>
+      <c r="AO37">
+        <v>80</v>
+      </c>
+      <c r="AP37">
+        <v>96</v>
+      </c>
+      <c r="AQ37">
+        <v>174</v>
+      </c>
+      <c r="AR37">
+        <v>193</v>
+      </c>
+      <c r="AS37">
+        <v>180</v>
+      </c>
+      <c r="AT37">
+        <v>251</v>
+      </c>
+      <c r="AU37">
+        <v>278</v>
+      </c>
+      <c r="AV37">
+        <v>292</v>
+      </c>
+      <c r="AW37">
+        <v>448</v>
+      </c>
+      <c r="AX37">
+        <v>518</v>
+      </c>
+      <c r="AY37">
+        <v>501</v>
+      </c>
+      <c r="AZ37">
+        <v>440</v>
+      </c>
+      <c r="BA37">
+        <v>328</v>
+      </c>
+      <c r="BB37">
+        <v>237</v>
+      </c>
+      <c r="BC37">
+        <v>185</v>
+      </c>
+      <c r="BD37">
+        <v>183</v>
+      </c>
+      <c r="BE37">
+        <v>106</v>
+      </c>
+      <c r="BF37">
+        <v>100</v>
+      </c>
+      <c r="BG37">
+        <v>60</v>
+      </c>
+      <c r="BH37">
+        <v>45</v>
+      </c>
+      <c r="BI37">
+        <v>43</v>
+      </c>
+      <c r="BJ37">
+        <v>22</v>
+      </c>
+      <c r="BK37">
+        <v>17</v>
+      </c>
+      <c r="BL37">
+        <v>13</v>
+      </c>
+      <c r="BM37">
+        <v>8</v>
+      </c>
+      <c r="BN37">
         <v>18</v>
-      </c>
-      <c r="AJ37">
-        <v>18</v>
-      </c>
-      <c r="AK37">
-        <v>22</v>
-      </c>
-      <c r="AL37">
-        <v>4</v>
-      </c>
-      <c r="AM37">
-        <v>8</v>
-      </c>
-      <c r="AN37">
-        <v>19</v>
-      </c>
-      <c r="AO37">
-        <v>34</v>
-      </c>
-      <c r="AP37">
-        <v>69</v>
-      </c>
-      <c r="AQ37">
-        <v>125</v>
-      </c>
-      <c r="AR37">
-        <v>143</v>
-      </c>
-      <c r="AS37">
-        <v>130</v>
-      </c>
-      <c r="AT37">
-        <v>154</v>
-      </c>
-      <c r="AU37">
-        <v>189</v>
-      </c>
-      <c r="AV37">
-        <v>254</v>
-      </c>
-      <c r="AW37">
-        <v>295</v>
-      </c>
-      <c r="AX37">
-        <v>346</v>
-      </c>
-      <c r="AY37">
-        <v>379</v>
-      </c>
-      <c r="AZ37">
-        <v>334</v>
-      </c>
-      <c r="BA37">
-        <v>264</v>
-      </c>
-      <c r="BB37">
-        <v>203</v>
-      </c>
-      <c r="BC37">
-        <v>140</v>
-      </c>
-      <c r="BD37">
-        <v>84</v>
-      </c>
-      <c r="BE37">
-        <v>50</v>
-      </c>
-      <c r="BF37">
-        <v>32</v>
-      </c>
-      <c r="BG37">
-        <v>17</v>
-      </c>
-      <c r="BH37">
-        <v>10</v>
-      </c>
-      <c r="BI37">
-        <v>8</v>
-      </c>
-      <c r="BJ37">
-        <v>4</v>
-      </c>
-      <c r="BK37">
-        <v>2</v>
-      </c>
-      <c r="BL37">
-        <v>0</v>
-      </c>
-      <c r="BM37">
-        <v>1</v>
-      </c>
-      <c r="BN37">
-        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:66" x14ac:dyDescent="0.3">
@@ -66192,7 +66212,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -66201,175 +66221,175 @@
         <v>200</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>12</v>
       </c>
       <c r="K38">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L38">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="M38">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="N38">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="O38">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="P38">
-        <v>345</v>
+        <v>154</v>
       </c>
       <c r="Q38">
-        <v>324</v>
+        <v>200</v>
       </c>
       <c r="R38">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="S38">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="T38">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="U38">
-        <v>359</v>
+        <v>462</v>
       </c>
       <c r="V38">
-        <v>374</v>
+        <v>586</v>
       </c>
       <c r="W38">
-        <v>408</v>
+        <v>801</v>
       </c>
       <c r="X38">
-        <v>532</v>
+        <v>985</v>
       </c>
       <c r="Y38">
-        <v>725</v>
+        <v>972</v>
       </c>
       <c r="Z38">
-        <v>720</v>
+        <v>876</v>
       </c>
       <c r="AA38">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="AB38">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="AC38">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="AD38">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="AE38">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="AF38">
+        <v>81</v>
+      </c>
+      <c r="AG38">
         <v>74</v>
       </c>
-      <c r="AG38">
-        <v>54</v>
-      </c>
       <c r="AH38">
+        <v>40</v>
+      </c>
+      <c r="AI38">
+        <v>18</v>
+      </c>
+      <c r="AJ38">
+        <v>18</v>
+      </c>
+      <c r="AK38">
+        <v>22</v>
+      </c>
+      <c r="AL38">
+        <v>4</v>
+      </c>
+      <c r="AM38">
+        <v>8</v>
+      </c>
+      <c r="AN38">
+        <v>19</v>
+      </c>
+      <c r="AO38">
         <v>34</v>
       </c>
-      <c r="AI38">
-        <v>19</v>
-      </c>
-      <c r="AJ38">
-        <v>13</v>
-      </c>
-      <c r="AK38">
-        <v>15</v>
-      </c>
-      <c r="AL38">
-        <v>7</v>
-      </c>
-      <c r="AM38">
-        <v>9</v>
-      </c>
-      <c r="AN38">
+      <c r="AP38">
+        <v>69</v>
+      </c>
+      <c r="AQ38">
+        <v>125</v>
+      </c>
+      <c r="AR38">
+        <v>143</v>
+      </c>
+      <c r="AS38">
+        <v>130</v>
+      </c>
+      <c r="AT38">
+        <v>154</v>
+      </c>
+      <c r="AU38">
+        <v>189</v>
+      </c>
+      <c r="AV38">
+        <v>254</v>
+      </c>
+      <c r="AW38">
+        <v>295</v>
+      </c>
+      <c r="AX38">
+        <v>346</v>
+      </c>
+      <c r="AY38">
+        <v>379</v>
+      </c>
+      <c r="AZ38">
+        <v>334</v>
+      </c>
+      <c r="BA38">
+        <v>264</v>
+      </c>
+      <c r="BB38">
+        <v>203</v>
+      </c>
+      <c r="BC38">
+        <v>140</v>
+      </c>
+      <c r="BD38">
+        <v>84</v>
+      </c>
+      <c r="BE38">
+        <v>50</v>
+      </c>
+      <c r="BF38">
         <v>32</v>
       </c>
-      <c r="AO38">
-        <v>52</v>
-      </c>
-      <c r="AP38">
-        <v>132</v>
-      </c>
-      <c r="AQ38">
-        <v>251</v>
-      </c>
-      <c r="AR38">
-        <v>359</v>
-      </c>
-      <c r="AS38">
-        <v>323</v>
-      </c>
-      <c r="AT38">
-        <v>274</v>
-      </c>
-      <c r="AU38">
-        <v>221</v>
-      </c>
-      <c r="AV38">
-        <v>249</v>
-      </c>
-      <c r="AW38">
-        <v>265</v>
-      </c>
-      <c r="AX38">
-        <v>331</v>
-      </c>
-      <c r="AY38">
-        <v>386</v>
-      </c>
-      <c r="AZ38">
-        <v>258</v>
-      </c>
-      <c r="BA38">
-        <v>142</v>
-      </c>
-      <c r="BB38">
-        <v>68</v>
-      </c>
-      <c r="BC38">
-        <v>74</v>
-      </c>
-      <c r="BD38">
-        <v>55</v>
-      </c>
-      <c r="BE38">
-        <v>41</v>
-      </c>
-      <c r="BF38">
-        <v>30</v>
-      </c>
       <c r="BG38">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BH38">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BI38">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BJ38">
         <v>4</v>
       </c>
       <c r="BK38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN38">
         <v>1</v>
@@ -66392,7 +66412,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -66401,178 +66421,178 @@
         <v>200</v>
       </c>
       <c r="I39">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J39">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K39">
         <v>38</v>
       </c>
       <c r="L39">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="M39">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="N39">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="O39">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="P39">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="Q39">
-        <v>522</v>
+        <v>324</v>
       </c>
       <c r="R39">
-        <v>737</v>
+        <v>285</v>
       </c>
       <c r="S39">
-        <v>728</v>
+        <v>310</v>
       </c>
       <c r="T39">
-        <v>679</v>
+        <v>344</v>
       </c>
       <c r="U39">
-        <v>574</v>
+        <v>359</v>
       </c>
       <c r="V39">
-        <v>534</v>
+        <v>374</v>
       </c>
       <c r="W39">
-        <v>601</v>
+        <v>408</v>
       </c>
       <c r="X39">
-        <v>664</v>
+        <v>532</v>
       </c>
       <c r="Y39">
-        <v>863</v>
+        <v>725</v>
       </c>
       <c r="Z39">
-        <v>971</v>
+        <v>720</v>
       </c>
       <c r="AA39">
-        <v>795</v>
+        <v>663</v>
       </c>
       <c r="AB39">
-        <v>685</v>
+        <v>482</v>
       </c>
       <c r="AC39">
-        <v>524</v>
+        <v>354</v>
       </c>
       <c r="AD39">
-        <v>396</v>
+        <v>186</v>
       </c>
       <c r="AE39">
-        <v>268</v>
+        <v>133</v>
       </c>
       <c r="AF39">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="AG39">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="AH39">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AI39">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AJ39">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AK39">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AL39">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AM39">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="AN39">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AO39">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="AP39">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="AQ39">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="AR39">
-        <v>207</v>
+        <v>359</v>
       </c>
       <c r="AS39">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="AT39">
-        <v>566</v>
+        <v>274</v>
       </c>
       <c r="AU39">
-        <v>574</v>
+        <v>221</v>
       </c>
       <c r="AV39">
-        <v>488</v>
+        <v>249</v>
       </c>
       <c r="AW39">
-        <v>426</v>
+        <v>265</v>
       </c>
       <c r="AX39">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="AY39">
-        <v>300</v>
+        <v>386</v>
       </c>
       <c r="AZ39">
-        <v>178</v>
+        <v>258</v>
       </c>
       <c r="BA39">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="BB39">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="BC39">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="BD39">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE39">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="BF39">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BG39">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH39">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="BI39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ39">
         <v>4</v>
       </c>
       <c r="BK39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM39">
         <v>0</v>
       </c>
       <c r="BN39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:66" x14ac:dyDescent="0.3">
@@ -66592,7 +66612,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -66601,175 +66621,175 @@
         <v>200</v>
       </c>
       <c r="I40">
+        <v>15</v>
+      </c>
+      <c r="J40">
+        <v>24</v>
+      </c>
+      <c r="K40">
+        <v>38</v>
+      </c>
+      <c r="L40">
+        <v>96</v>
+      </c>
+      <c r="M40">
+        <v>140</v>
+      </c>
+      <c r="N40">
+        <v>200</v>
+      </c>
+      <c r="O40">
+        <v>269</v>
+      </c>
+      <c r="P40">
+        <v>361</v>
+      </c>
+      <c r="Q40">
+        <v>522</v>
+      </c>
+      <c r="R40">
+        <v>737</v>
+      </c>
+      <c r="S40">
+        <v>728</v>
+      </c>
+      <c r="T40">
+        <v>679</v>
+      </c>
+      <c r="U40">
+        <v>574</v>
+      </c>
+      <c r="V40">
+        <v>534</v>
+      </c>
+      <c r="W40">
+        <v>601</v>
+      </c>
+      <c r="X40">
+        <v>664</v>
+      </c>
+      <c r="Y40">
+        <v>863</v>
+      </c>
+      <c r="Z40">
+        <v>971</v>
+      </c>
+      <c r="AA40">
+        <v>795</v>
+      </c>
+      <c r="AB40">
+        <v>685</v>
+      </c>
+      <c r="AC40">
+        <v>524</v>
+      </c>
+      <c r="AD40">
+        <v>396</v>
+      </c>
+      <c r="AE40">
+        <v>268</v>
+      </c>
+      <c r="AF40">
+        <v>157</v>
+      </c>
+      <c r="AG40">
+        <v>103</v>
+      </c>
+      <c r="AH40">
+        <v>70</v>
+      </c>
+      <c r="AI40">
+        <v>36</v>
+      </c>
+      <c r="AJ40">
+        <v>27</v>
+      </c>
+      <c r="AK40">
+        <v>26</v>
+      </c>
+      <c r="AL40">
         <v>13</v>
       </c>
-      <c r="J40">
-        <v>34</v>
-      </c>
-      <c r="K40">
-        <v>43</v>
-      </c>
-      <c r="L40">
-        <v>56</v>
-      </c>
-      <c r="M40">
+      <c r="AM40">
+        <v>27</v>
+      </c>
+      <c r="AN40">
+        <v>50</v>
+      </c>
+      <c r="AO40">
+        <v>91</v>
+      </c>
+      <c r="AP40">
+        <v>141</v>
+      </c>
+      <c r="AQ40">
+        <v>181</v>
+      </c>
+      <c r="AR40">
+        <v>207</v>
+      </c>
+      <c r="AS40">
+        <v>356</v>
+      </c>
+      <c r="AT40">
+        <v>566</v>
+      </c>
+      <c r="AU40">
+        <v>574</v>
+      </c>
+      <c r="AV40">
+        <v>488</v>
+      </c>
+      <c r="AW40">
+        <v>426</v>
+      </c>
+      <c r="AX40">
+        <v>387</v>
+      </c>
+      <c r="AY40">
+        <v>300</v>
+      </c>
+      <c r="AZ40">
+        <v>178</v>
+      </c>
+      <c r="BA40">
+        <v>109</v>
+      </c>
+      <c r="BB40">
         <v>65</v>
       </c>
-      <c r="N40">
-        <v>90</v>
-      </c>
-      <c r="O40">
-        <v>115</v>
-      </c>
-      <c r="P40">
-        <v>122</v>
-      </c>
-      <c r="Q40">
-        <v>132</v>
-      </c>
-      <c r="R40">
-        <v>175</v>
-      </c>
-      <c r="S40">
-        <v>213</v>
-      </c>
-      <c r="T40">
-        <v>294</v>
-      </c>
-      <c r="U40">
-        <v>324</v>
-      </c>
-      <c r="V40">
-        <v>352</v>
-      </c>
-      <c r="W40">
-        <v>313</v>
-      </c>
-      <c r="X40">
-        <v>255</v>
-      </c>
-      <c r="Y40">
-        <v>230</v>
-      </c>
-      <c r="Z40">
-        <v>241</v>
-      </c>
-      <c r="AA40">
-        <v>229</v>
-      </c>
-      <c r="AB40">
-        <v>209</v>
-      </c>
-      <c r="AC40">
-        <v>210</v>
-      </c>
-      <c r="AD40">
-        <v>169</v>
-      </c>
-      <c r="AE40">
-        <v>128</v>
-      </c>
-      <c r="AF40">
-        <v>106</v>
-      </c>
-      <c r="AG40">
-        <v>74</v>
-      </c>
-      <c r="AH40">
-        <v>39</v>
-      </c>
-      <c r="AI40">
-        <v>29</v>
-      </c>
-      <c r="AJ40">
-        <v>15</v>
-      </c>
-      <c r="AK40">
-        <v>13</v>
-      </c>
-      <c r="AL40">
-        <v>42</v>
-      </c>
-      <c r="AM40">
-        <v>54</v>
-      </c>
-      <c r="AN40">
-        <v>69</v>
-      </c>
-      <c r="AO40">
-        <v>75</v>
-      </c>
-      <c r="AP40">
-        <v>123</v>
-      </c>
-      <c r="AQ40">
-        <v>151</v>
-      </c>
-      <c r="AR40">
-        <v>161</v>
-      </c>
-      <c r="AS40">
-        <v>182</v>
-      </c>
-      <c r="AT40">
-        <v>208</v>
-      </c>
-      <c r="AU40">
-        <v>255</v>
-      </c>
-      <c r="AV40">
-        <v>291</v>
-      </c>
-      <c r="AW40">
-        <v>299</v>
-      </c>
-      <c r="AX40">
-        <v>213</v>
-      </c>
-      <c r="AY40">
-        <v>171</v>
-      </c>
-      <c r="AZ40">
-        <v>111</v>
-      </c>
-      <c r="BA40">
-        <v>82</v>
-      </c>
-      <c r="BB40">
-        <v>42</v>
-      </c>
       <c r="BC40">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="BD40">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BE40">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="BF40">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="BG40">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BH40">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BI40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BJ40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BK40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN40">
         <v>0</v>
@@ -66792,7 +66812,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -66801,172 +66821,172 @@
         <v>200</v>
       </c>
       <c r="I41">
+        <v>13</v>
+      </c>
+      <c r="J41">
+        <v>34</v>
+      </c>
+      <c r="K41">
+        <v>43</v>
+      </c>
+      <c r="L41">
+        <v>56</v>
+      </c>
+      <c r="M41">
+        <v>65</v>
+      </c>
+      <c r="N41">
+        <v>90</v>
+      </c>
+      <c r="O41">
+        <v>115</v>
+      </c>
+      <c r="P41">
+        <v>122</v>
+      </c>
+      <c r="Q41">
+        <v>132</v>
+      </c>
+      <c r="R41">
+        <v>175</v>
+      </c>
+      <c r="S41">
+        <v>213</v>
+      </c>
+      <c r="T41">
+        <v>294</v>
+      </c>
+      <c r="U41">
+        <v>324</v>
+      </c>
+      <c r="V41">
+        <v>352</v>
+      </c>
+      <c r="W41">
+        <v>313</v>
+      </c>
+      <c r="X41">
+        <v>255</v>
+      </c>
+      <c r="Y41">
+        <v>230</v>
+      </c>
+      <c r="Z41">
+        <v>241</v>
+      </c>
+      <c r="AA41">
+        <v>229</v>
+      </c>
+      <c r="AB41">
+        <v>209</v>
+      </c>
+      <c r="AC41">
+        <v>210</v>
+      </c>
+      <c r="AD41">
+        <v>169</v>
+      </c>
+      <c r="AE41">
+        <v>128</v>
+      </c>
+      <c r="AF41">
+        <v>106</v>
+      </c>
+      <c r="AG41">
+        <v>74</v>
+      </c>
+      <c r="AH41">
+        <v>39</v>
+      </c>
+      <c r="AI41">
+        <v>29</v>
+      </c>
+      <c r="AJ41">
+        <v>15</v>
+      </c>
+      <c r="AK41">
+        <v>13</v>
+      </c>
+      <c r="AL41">
+        <v>42</v>
+      </c>
+      <c r="AM41">
+        <v>54</v>
+      </c>
+      <c r="AN41">
+        <v>69</v>
+      </c>
+      <c r="AO41">
+        <v>75</v>
+      </c>
+      <c r="AP41">
+        <v>123</v>
+      </c>
+      <c r="AQ41">
+        <v>151</v>
+      </c>
+      <c r="AR41">
+        <v>161</v>
+      </c>
+      <c r="AS41">
+        <v>182</v>
+      </c>
+      <c r="AT41">
+        <v>208</v>
+      </c>
+      <c r="AU41">
+        <v>255</v>
+      </c>
+      <c r="AV41">
+        <v>291</v>
+      </c>
+      <c r="AW41">
+        <v>299</v>
+      </c>
+      <c r="AX41">
+        <v>213</v>
+      </c>
+      <c r="AY41">
+        <v>171</v>
+      </c>
+      <c r="AZ41">
+        <v>111</v>
+      </c>
+      <c r="BA41">
+        <v>82</v>
+      </c>
+      <c r="BB41">
+        <v>42</v>
+      </c>
+      <c r="BC41">
+        <v>34</v>
+      </c>
+      <c r="BD41">
+        <v>24</v>
+      </c>
+      <c r="BE41">
+        <v>21</v>
+      </c>
+      <c r="BF41">
+        <v>17</v>
+      </c>
+      <c r="BG41">
+        <v>17</v>
+      </c>
+      <c r="BH41">
         <v>8</v>
       </c>
-      <c r="J41">
-        <v>22</v>
-      </c>
-      <c r="K41">
-        <v>28</v>
-      </c>
-      <c r="L41">
-        <v>40</v>
-      </c>
-      <c r="M41">
-        <v>83</v>
-      </c>
-      <c r="N41">
-        <v>121</v>
-      </c>
-      <c r="O41">
-        <v>147</v>
-      </c>
-      <c r="P41">
-        <v>159</v>
-      </c>
-      <c r="Q41">
-        <v>167</v>
-      </c>
-      <c r="R41">
-        <v>217</v>
-      </c>
-      <c r="S41">
-        <v>272</v>
-      </c>
-      <c r="T41">
-        <v>362</v>
-      </c>
-      <c r="U41">
-        <v>500</v>
-      </c>
-      <c r="V41">
-        <v>631</v>
-      </c>
-      <c r="W41">
-        <v>768</v>
-      </c>
-      <c r="X41">
-        <v>703</v>
-      </c>
-      <c r="Y41">
-        <v>645</v>
-      </c>
-      <c r="Z41">
-        <v>476</v>
-      </c>
-      <c r="AA41">
-        <v>400</v>
-      </c>
-      <c r="AB41">
-        <v>352</v>
-      </c>
-      <c r="AC41">
-        <v>315</v>
-      </c>
-      <c r="AD41">
-        <v>186</v>
-      </c>
-      <c r="AE41">
-        <v>129</v>
-      </c>
-      <c r="AF41">
-        <v>98</v>
-      </c>
-      <c r="AG41">
-        <v>50</v>
-      </c>
-      <c r="AH41">
-        <v>38</v>
-      </c>
-      <c r="AI41">
-        <v>15</v>
-      </c>
-      <c r="AJ41">
-        <v>7</v>
-      </c>
-      <c r="AK41">
+      <c r="BI41">
+        <v>9</v>
+      </c>
+      <c r="BJ41">
         <v>8</v>
       </c>
-      <c r="AL41">
-        <v>6</v>
-      </c>
-      <c r="AM41">
-        <v>10</v>
-      </c>
-      <c r="AN41">
-        <v>21</v>
-      </c>
-      <c r="AO41">
-        <v>60</v>
-      </c>
-      <c r="AP41">
-        <v>80</v>
-      </c>
-      <c r="AQ41">
-        <v>118</v>
-      </c>
-      <c r="AR41">
-        <v>162</v>
-      </c>
-      <c r="AS41">
-        <v>181</v>
-      </c>
-      <c r="AT41">
-        <v>203</v>
-      </c>
-      <c r="AU41">
-        <v>234</v>
-      </c>
-      <c r="AV41">
-        <v>242</v>
-      </c>
-      <c r="AW41">
-        <v>221</v>
-      </c>
-      <c r="AX41">
-        <v>200</v>
-      </c>
-      <c r="AY41">
-        <v>188</v>
-      </c>
-      <c r="AZ41">
-        <v>115</v>
-      </c>
-      <c r="BA41">
-        <v>83</v>
-      </c>
-      <c r="BB41">
-        <v>44</v>
-      </c>
-      <c r="BC41">
-        <v>29</v>
-      </c>
-      <c r="BD41">
-        <v>16</v>
-      </c>
-      <c r="BE41">
-        <v>13</v>
-      </c>
-      <c r="BF41">
-        <v>12</v>
-      </c>
-      <c r="BG41">
-        <v>11</v>
-      </c>
-      <c r="BH41">
-        <v>6</v>
-      </c>
-      <c r="BI41">
-        <v>4</v>
-      </c>
-      <c r="BJ41">
-        <v>3</v>
-      </c>
       <c r="BK41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM41">
         <v>1</v>
@@ -66992,7 +67012,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -67001,175 +67021,175 @@
         <v>200</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K42">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L42">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M42">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="N42">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="O42">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="P42">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="Q42">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="R42">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="S42">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="T42">
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="U42">
-        <v>321</v>
+        <v>500</v>
       </c>
       <c r="V42">
-        <v>460</v>
+        <v>631</v>
       </c>
       <c r="W42">
-        <v>650</v>
+        <v>768</v>
       </c>
       <c r="X42">
-        <v>643</v>
+        <v>703</v>
       </c>
       <c r="Y42">
-        <v>484</v>
+        <v>645</v>
       </c>
       <c r="Z42">
-        <v>357</v>
+        <v>476</v>
       </c>
       <c r="AA42">
-        <v>216</v>
+        <v>400</v>
       </c>
       <c r="AB42">
-        <v>194</v>
+        <v>352</v>
       </c>
       <c r="AC42">
-        <v>147</v>
+        <v>315</v>
       </c>
       <c r="AD42">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="AE42">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="AF42">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="AG42">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AH42">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AI42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ42">
         <v>7</v>
       </c>
       <c r="AK42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM42">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AN42">
         <v>21</v>
       </c>
       <c r="AO42">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="AP42">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="AQ42">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AR42">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="AS42">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="AT42">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="AU42">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AV42">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="AW42">
-        <v>278</v>
+        <v>221</v>
       </c>
       <c r="AX42">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AY42">
-        <v>117</v>
+        <v>188</v>
       </c>
       <c r="AZ42">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="BA42">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="BB42">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="BC42">
+        <v>29</v>
+      </c>
+      <c r="BD42">
+        <v>16</v>
+      </c>
+      <c r="BE42">
         <v>13</v>
       </c>
-      <c r="BD42">
+      <c r="BF42">
+        <v>12</v>
+      </c>
+      <c r="BG42">
         <v>11</v>
       </c>
-      <c r="BE42">
+      <c r="BH42">
         <v>6</v>
       </c>
-      <c r="BF42">
+      <c r="BI42">
         <v>4</v>
       </c>
-      <c r="BG42">
-        <v>4</v>
-      </c>
-      <c r="BH42">
-        <v>2</v>
-      </c>
-      <c r="BI42">
-        <v>2</v>
-      </c>
       <c r="BJ42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL42">
         <v>0</v>
       </c>
       <c r="BM42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN42">
         <v>0</v>
@@ -67192,7 +67212,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -67201,175 +67221,175 @@
         <v>200</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K43">
+        <v>12</v>
+      </c>
+      <c r="L43">
+        <v>30</v>
+      </c>
+      <c r="M43">
+        <v>47</v>
+      </c>
+      <c r="N43">
+        <v>78</v>
+      </c>
+      <c r="O43">
+        <v>110</v>
+      </c>
+      <c r="P43">
+        <v>133</v>
+      </c>
+      <c r="Q43">
+        <v>149</v>
+      </c>
+      <c r="R43">
+        <v>183</v>
+      </c>
+      <c r="S43">
+        <v>194</v>
+      </c>
+      <c r="T43">
+        <v>268</v>
+      </c>
+      <c r="U43">
+        <v>321</v>
+      </c>
+      <c r="V43">
+        <v>460</v>
+      </c>
+      <c r="W43">
+        <v>650</v>
+      </c>
+      <c r="X43">
+        <v>643</v>
+      </c>
+      <c r="Y43">
+        <v>484</v>
+      </c>
+      <c r="Z43">
+        <v>357</v>
+      </c>
+      <c r="AA43">
+        <v>216</v>
+      </c>
+      <c r="AB43">
+        <v>194</v>
+      </c>
+      <c r="AC43">
+        <v>147</v>
+      </c>
+      <c r="AD43">
+        <v>102</v>
+      </c>
+      <c r="AE43">
+        <v>88</v>
+      </c>
+      <c r="AF43">
+        <v>48</v>
+      </c>
+      <c r="AG43">
+        <v>70</v>
+      </c>
+      <c r="AH43">
+        <v>29</v>
+      </c>
+      <c r="AI43">
+        <v>12</v>
+      </c>
+      <c r="AJ43">
         <v>7</v>
       </c>
-      <c r="L43">
-        <v>28</v>
-      </c>
-      <c r="M43">
-        <v>65</v>
-      </c>
-      <c r="N43">
-        <v>134</v>
-      </c>
-      <c r="O43">
+      <c r="AK43">
+        <v>4</v>
+      </c>
+      <c r="AL43">
+        <v>8</v>
+      </c>
+      <c r="AM43">
+        <v>20</v>
+      </c>
+      <c r="AN43">
+        <v>21</v>
+      </c>
+      <c r="AO43">
+        <v>43</v>
+      </c>
+      <c r="AP43">
+        <v>66</v>
+      </c>
+      <c r="AQ43">
+        <v>119</v>
+      </c>
+      <c r="AR43">
         <v>145</v>
       </c>
-      <c r="P43">
-        <v>200</v>
-      </c>
-      <c r="Q43">
-        <v>266</v>
-      </c>
-      <c r="R43">
-        <v>327</v>
-      </c>
-      <c r="S43">
-        <v>270</v>
-      </c>
-      <c r="T43">
-        <v>247</v>
-      </c>
-      <c r="U43">
-        <v>238</v>
-      </c>
-      <c r="V43">
-        <v>317</v>
-      </c>
-      <c r="W43">
-        <v>371</v>
-      </c>
-      <c r="X43">
-        <v>469</v>
-      </c>
-      <c r="Y43">
-        <v>402</v>
-      </c>
-      <c r="Z43">
-        <v>331</v>
-      </c>
-      <c r="AA43">
-        <v>170</v>
-      </c>
-      <c r="AB43">
-        <v>114</v>
-      </c>
-      <c r="AC43">
-        <v>85</v>
-      </c>
-      <c r="AD43">
-        <v>65</v>
-      </c>
-      <c r="AE43">
-        <v>54</v>
-      </c>
-      <c r="AF43">
-        <v>51</v>
-      </c>
-      <c r="AG43">
-        <v>46</v>
-      </c>
-      <c r="AH43">
-        <v>24</v>
-      </c>
-      <c r="AI43">
-        <v>9</v>
-      </c>
-      <c r="AJ43">
-        <v>3</v>
-      </c>
-      <c r="AK43">
-        <v>5</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>5</v>
-      </c>
-      <c r="AN43">
-        <v>9</v>
-      </c>
-      <c r="AO43">
+      <c r="AS43">
+        <v>171</v>
+      </c>
+      <c r="AT43">
+        <v>194</v>
+      </c>
+      <c r="AU43">
+        <v>228</v>
+      </c>
+      <c r="AV43">
+        <v>295</v>
+      </c>
+      <c r="AW43">
+        <v>278</v>
+      </c>
+      <c r="AX43">
+        <v>203</v>
+      </c>
+      <c r="AY43">
+        <v>117</v>
+      </c>
+      <c r="AZ43">
+        <v>91</v>
+      </c>
+      <c r="BA43">
+        <v>56</v>
+      </c>
+      <c r="BB43">
         <v>18</v>
       </c>
-      <c r="AP43">
-        <v>53</v>
-      </c>
-      <c r="AQ43">
-        <v>127</v>
-      </c>
-      <c r="AR43">
-        <v>168</v>
-      </c>
-      <c r="AS43">
-        <v>182</v>
-      </c>
-      <c r="AT43">
-        <v>242</v>
-      </c>
-      <c r="AU43">
-        <v>260</v>
-      </c>
-      <c r="AV43">
-        <v>245</v>
-      </c>
-      <c r="AW43">
-        <v>277</v>
-      </c>
-      <c r="AX43">
-        <v>217</v>
-      </c>
-      <c r="AY43">
-        <v>184</v>
-      </c>
-      <c r="AZ43">
-        <v>120</v>
-      </c>
-      <c r="BA43">
-        <v>83</v>
-      </c>
-      <c r="BB43">
-        <v>45</v>
-      </c>
       <c r="BC43">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BD43">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BE43">
         <v>6</v>
       </c>
       <c r="BF43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BG43">
         <v>4</v>
       </c>
       <c r="BH43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BI43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL43">
         <v>0</v>
       </c>
       <c r="BM43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN43">
         <v>0</v>
@@ -67392,7 +67412,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -67401,172 +67421,172 @@
         <v>200</v>
       </c>
       <c r="I44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L44">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M44">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="N44">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="O44">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="P44">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="Q44">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="R44">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="S44">
-        <v>461</v>
+        <v>270</v>
       </c>
       <c r="T44">
-        <v>514</v>
+        <v>247</v>
       </c>
       <c r="U44">
-        <v>490</v>
+        <v>238</v>
       </c>
       <c r="V44">
-        <v>478</v>
+        <v>317</v>
       </c>
       <c r="W44">
-        <v>540</v>
+        <v>371</v>
       </c>
       <c r="X44">
-        <v>518</v>
+        <v>469</v>
       </c>
       <c r="Y44">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="Z44">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="AA44">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="AB44">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="AC44">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="AD44">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="AE44">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AF44">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AG44">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="AH44">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AI44">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AJ44">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AK44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM44">
         <v>5</v>
       </c>
       <c r="AN44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO44">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AP44">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="AQ44">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="AR44">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="AS44">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AT44">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="AU44">
-        <v>401</v>
+        <v>260</v>
       </c>
       <c r="AV44">
-        <v>450</v>
+        <v>245</v>
       </c>
       <c r="AW44">
-        <v>396</v>
+        <v>277</v>
       </c>
       <c r="AX44">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="AY44">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="AZ44">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="BA44">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="BB44">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="BC44">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BD44">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BE44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BF44">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BG44">
         <v>4</v>
       </c>
       <c r="BH44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM44">
         <v>1</v>
@@ -67592,7 +67612,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -67601,166 +67621,166 @@
         <v>200</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45">
+        <v>8</v>
+      </c>
+      <c r="L45">
+        <v>15</v>
+      </c>
+      <c r="M45">
+        <v>41</v>
+      </c>
+      <c r="N45">
+        <v>56</v>
+      </c>
+      <c r="O45">
+        <v>104</v>
+      </c>
+      <c r="P45">
+        <v>162</v>
+      </c>
+      <c r="Q45">
+        <v>239</v>
+      </c>
+      <c r="R45">
+        <v>373</v>
+      </c>
+      <c r="S45">
+        <v>461</v>
+      </c>
+      <c r="T45">
+        <v>514</v>
+      </c>
+      <c r="U45">
+        <v>490</v>
+      </c>
+      <c r="V45">
+        <v>478</v>
+      </c>
+      <c r="W45">
+        <v>540</v>
+      </c>
+      <c r="X45">
+        <v>518</v>
+      </c>
+      <c r="Y45">
+        <v>459</v>
+      </c>
+      <c r="Z45">
+        <v>350</v>
+      </c>
+      <c r="AA45">
+        <v>236</v>
+      </c>
+      <c r="AB45">
+        <v>140</v>
+      </c>
+      <c r="AC45">
+        <v>96</v>
+      </c>
+      <c r="AD45">
+        <v>71</v>
+      </c>
+      <c r="AE45">
+        <v>48</v>
+      </c>
+      <c r="AF45">
+        <v>53</v>
+      </c>
+      <c r="AG45">
+        <v>62</v>
+      </c>
+      <c r="AH45">
+        <v>38</v>
+      </c>
+      <c r="AI45">
+        <v>21</v>
+      </c>
+      <c r="AJ45">
+        <v>12</v>
+      </c>
+      <c r="AK45">
+        <v>3</v>
+      </c>
+      <c r="AL45">
+        <v>2</v>
+      </c>
+      <c r="AM45">
         <v>5</v>
-      </c>
-      <c r="L45">
-        <v>17</v>
-      </c>
-      <c r="M45">
-        <v>38</v>
-      </c>
-      <c r="N45">
-        <v>62</v>
-      </c>
-      <c r="O45">
-        <v>98</v>
-      </c>
-      <c r="P45">
-        <v>124</v>
-      </c>
-      <c r="Q45">
-        <v>133</v>
-      </c>
-      <c r="R45">
-        <v>231</v>
-      </c>
-      <c r="S45">
-        <v>281</v>
-      </c>
-      <c r="T45">
-        <v>369</v>
-      </c>
-      <c r="U45">
-        <v>400</v>
-      </c>
-      <c r="V45">
-        <v>412</v>
-      </c>
-      <c r="W45">
-        <v>352</v>
-      </c>
-      <c r="X45">
-        <v>298</v>
-      </c>
-      <c r="Y45">
-        <v>299</v>
-      </c>
-      <c r="Z45">
-        <v>231</v>
-      </c>
-      <c r="AA45">
-        <v>160</v>
-      </c>
-      <c r="AB45">
-        <v>111</v>
-      </c>
-      <c r="AC45">
-        <v>59</v>
-      </c>
-      <c r="AD45">
-        <v>31</v>
-      </c>
-      <c r="AE45">
-        <v>22</v>
-      </c>
-      <c r="AF45">
-        <v>22</v>
-      </c>
-      <c r="AG45">
-        <v>15</v>
-      </c>
-      <c r="AH45">
-        <v>13</v>
-      </c>
-      <c r="AI45">
-        <v>11</v>
-      </c>
-      <c r="AJ45">
-        <v>4</v>
-      </c>
-      <c r="AK45">
-        <v>2</v>
-      </c>
-      <c r="AL45">
-        <v>0</v>
-      </c>
-      <c r="AM45">
-        <v>3</v>
       </c>
       <c r="AN45">
         <v>8</v>
       </c>
       <c r="AO45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP45">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AQ45">
         <v>72</v>
       </c>
       <c r="AR45">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="AS45">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="AT45">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="AU45">
-        <v>242</v>
+        <v>401</v>
       </c>
       <c r="AV45">
-        <v>318</v>
+        <v>450</v>
       </c>
       <c r="AW45">
-        <v>329</v>
+        <v>396</v>
       </c>
       <c r="AX45">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="AY45">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="AZ45">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="BA45">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="BB45">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="BC45">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BD45">
+        <v>11</v>
+      </c>
+      <c r="BE45">
         <v>10</v>
-      </c>
-      <c r="BE45">
-        <v>4</v>
       </c>
       <c r="BF45">
         <v>6</v>
       </c>
       <c r="BG45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BH45">
+        <v>2</v>
+      </c>
+      <c r="BI45">
         <v>3</v>
       </c>
-      <c r="BI45">
-        <v>2</v>
-      </c>
       <c r="BJ45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK45">
         <v>2</v>
@@ -67769,7 +67789,7 @@
         <v>1</v>
       </c>
       <c r="BM45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN45">
         <v>0</v>
@@ -67792,7 +67812,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -67801,157 +67821,157 @@
         <v>200</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>4</v>
       </c>
       <c r="K46">
+        <v>5</v>
+      </c>
+      <c r="L46">
+        <v>17</v>
+      </c>
+      <c r="M46">
+        <v>38</v>
+      </c>
+      <c r="N46">
+        <v>62</v>
+      </c>
+      <c r="O46">
+        <v>98</v>
+      </c>
+      <c r="P46">
+        <v>124</v>
+      </c>
+      <c r="Q46">
+        <v>133</v>
+      </c>
+      <c r="R46">
+        <v>231</v>
+      </c>
+      <c r="S46">
+        <v>281</v>
+      </c>
+      <c r="T46">
+        <v>369</v>
+      </c>
+      <c r="U46">
+        <v>400</v>
+      </c>
+      <c r="V46">
+        <v>412</v>
+      </c>
+      <c r="W46">
+        <v>352</v>
+      </c>
+      <c r="X46">
+        <v>298</v>
+      </c>
+      <c r="Y46">
+        <v>299</v>
+      </c>
+      <c r="Z46">
+        <v>231</v>
+      </c>
+      <c r="AA46">
+        <v>160</v>
+      </c>
+      <c r="AB46">
+        <v>111</v>
+      </c>
+      <c r="AC46">
+        <v>59</v>
+      </c>
+      <c r="AD46">
+        <v>31</v>
+      </c>
+      <c r="AE46">
         <v>22</v>
       </c>
-      <c r="L46">
-        <v>14</v>
-      </c>
-      <c r="M46">
+      <c r="AF46">
+        <v>22</v>
+      </c>
+      <c r="AG46">
         <v>15</v>
       </c>
-      <c r="N46">
-        <v>54</v>
-      </c>
-      <c r="O46">
-        <v>95</v>
-      </c>
-      <c r="P46">
-        <v>176</v>
-      </c>
-      <c r="Q46">
-        <v>269</v>
-      </c>
-      <c r="R46">
-        <v>389</v>
-      </c>
-      <c r="S46">
-        <v>522</v>
-      </c>
-      <c r="T46">
-        <v>684</v>
-      </c>
-      <c r="U46">
-        <v>754</v>
-      </c>
-      <c r="V46">
-        <v>844</v>
-      </c>
-      <c r="W46">
-        <v>822</v>
-      </c>
-      <c r="X46">
-        <v>774</v>
-      </c>
-      <c r="Y46">
-        <v>594</v>
-      </c>
-      <c r="Z46">
-        <v>442</v>
-      </c>
-      <c r="AA46">
-        <v>330</v>
-      </c>
-      <c r="AB46">
-        <v>217</v>
-      </c>
-      <c r="AC46">
-        <v>136</v>
-      </c>
-      <c r="AD46">
-        <v>90</v>
-      </c>
-      <c r="AE46">
-        <v>59</v>
-      </c>
-      <c r="AF46">
-        <v>20</v>
-      </c>
-      <c r="AG46">
-        <v>18</v>
-      </c>
       <c r="AH46">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AI46">
+        <v>11</v>
+      </c>
+      <c r="AJ46">
+        <v>4</v>
+      </c>
+      <c r="AK46">
+        <v>2</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>3</v>
+      </c>
+      <c r="AN46">
+        <v>8</v>
+      </c>
+      <c r="AO46">
         <v>13</v>
       </c>
-      <c r="AJ46">
-        <v>3</v>
-      </c>
-      <c r="AK46">
-        <v>8</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>5</v>
-      </c>
-      <c r="AN46">
-        <v>17</v>
-      </c>
-      <c r="AO46">
-        <v>7</v>
-      </c>
       <c r="AP46">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AQ46">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="AR46">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="AS46">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="AT46">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="AU46">
-        <v>457</v>
+        <v>242</v>
       </c>
       <c r="AV46">
-        <v>577</v>
+        <v>318</v>
       </c>
       <c r="AW46">
-        <v>560</v>
+        <v>329</v>
       </c>
       <c r="AX46">
-        <v>394</v>
+        <v>246</v>
       </c>
       <c r="AY46">
-        <v>236</v>
+        <v>141</v>
       </c>
       <c r="AZ46">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="BA46">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="BB46">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="BC46">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="BD46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BE46">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BF46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BG46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH46">
         <v>3</v>
@@ -67960,18 +67980,418 @@
         <v>2</v>
       </c>
       <c r="BJ46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:66" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>281</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>2024</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>200</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47">
+        <v>22</v>
+      </c>
+      <c r="L47">
+        <v>14</v>
+      </c>
+      <c r="M47">
+        <v>15</v>
+      </c>
+      <c r="N47">
+        <v>54</v>
+      </c>
+      <c r="O47">
+        <v>95</v>
+      </c>
+      <c r="P47">
+        <v>176</v>
+      </c>
+      <c r="Q47">
+        <v>269</v>
+      </c>
+      <c r="R47">
+        <v>389</v>
+      </c>
+      <c r="S47">
+        <v>522</v>
+      </c>
+      <c r="T47">
+        <v>684</v>
+      </c>
+      <c r="U47">
+        <v>754</v>
+      </c>
+      <c r="V47">
+        <v>844</v>
+      </c>
+      <c r="W47">
+        <v>822</v>
+      </c>
+      <c r="X47">
+        <v>774</v>
+      </c>
+      <c r="Y47">
+        <v>594</v>
+      </c>
+      <c r="Z47">
+        <v>442</v>
+      </c>
+      <c r="AA47">
+        <v>330</v>
+      </c>
+      <c r="AB47">
+        <v>217</v>
+      </c>
+      <c r="AC47">
+        <v>136</v>
+      </c>
+      <c r="AD47">
+        <v>90</v>
+      </c>
+      <c r="AE47">
+        <v>59</v>
+      </c>
+      <c r="AF47">
+        <v>20</v>
+      </c>
+      <c r="AG47">
+        <v>18</v>
+      </c>
+      <c r="AH47">
+        <v>20</v>
+      </c>
+      <c r="AI47">
+        <v>13</v>
+      </c>
+      <c r="AJ47">
+        <v>3</v>
+      </c>
+      <c r="AK47">
+        <v>8</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>5</v>
+      </c>
+      <c r="AN47">
+        <v>17</v>
+      </c>
+      <c r="AO47">
+        <v>7</v>
+      </c>
+      <c r="AP47">
+        <v>26</v>
+      </c>
+      <c r="AQ47">
+        <v>81</v>
+      </c>
+      <c r="AR47">
+        <v>150</v>
+      </c>
+      <c r="AS47">
+        <v>257</v>
+      </c>
+      <c r="AT47">
+        <v>340</v>
+      </c>
+      <c r="AU47">
+        <v>457</v>
+      </c>
+      <c r="AV47">
+        <v>577</v>
+      </c>
+      <c r="AW47">
+        <v>560</v>
+      </c>
+      <c r="AX47">
+        <v>394</v>
+      </c>
+      <c r="AY47">
+        <v>236</v>
+      </c>
+      <c r="AZ47">
+        <v>123</v>
+      </c>
+      <c r="BA47">
+        <v>67</v>
+      </c>
+      <c r="BB47">
+        <v>35</v>
+      </c>
+      <c r="BC47">
+        <v>29</v>
+      </c>
+      <c r="BD47">
+        <v>13</v>
+      </c>
+      <c r="BE47">
+        <v>11</v>
+      </c>
+      <c r="BF47">
+        <v>7</v>
+      </c>
+      <c r="BG47">
+        <v>3</v>
+      </c>
+      <c r="BH47">
+        <v>3</v>
+      </c>
+      <c r="BI47">
+        <v>2</v>
+      </c>
+      <c r="BJ47">
+        <v>1</v>
+      </c>
+      <c r="BK47">
+        <v>0</v>
+      </c>
+      <c r="BL47">
+        <v>0</v>
+      </c>
+      <c r="BM47">
+        <v>1</v>
+      </c>
+      <c r="BN47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:66" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>281</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>2025</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>200</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>5</v>
+      </c>
+      <c r="L48">
+        <v>18</v>
+      </c>
+      <c r="M48">
+        <v>28</v>
+      </c>
+      <c r="N48">
+        <v>54</v>
+      </c>
+      <c r="O48">
+        <v>118</v>
+      </c>
+      <c r="P48">
+        <v>130</v>
+      </c>
+      <c r="Q48">
+        <v>134</v>
+      </c>
+      <c r="R48">
+        <v>194</v>
+      </c>
+      <c r="S48">
+        <v>277</v>
+      </c>
+      <c r="T48">
+        <v>361</v>
+      </c>
+      <c r="U48">
+        <v>392</v>
+      </c>
+      <c r="V48">
+        <v>589</v>
+      </c>
+      <c r="W48">
+        <v>658</v>
+      </c>
+      <c r="X48">
+        <v>649</v>
+      </c>
+      <c r="Y48">
+        <v>541</v>
+      </c>
+      <c r="Z48">
+        <v>407</v>
+      </c>
+      <c r="AA48">
+        <v>300</v>
+      </c>
+      <c r="AB48">
+        <v>190</v>
+      </c>
+      <c r="AC48">
+        <v>92</v>
+      </c>
+      <c r="AD48">
+        <v>62</v>
+      </c>
+      <c r="AE48">
+        <v>29</v>
+      </c>
+      <c r="AF48">
+        <v>28</v>
+      </c>
+      <c r="AG48">
+        <v>16</v>
+      </c>
+      <c r="AH48">
+        <v>16</v>
+      </c>
+      <c r="AI48">
+        <v>11</v>
+      </c>
+      <c r="AJ48">
+        <v>4</v>
+      </c>
+      <c r="AK48">
+        <v>9</v>
+      </c>
+      <c r="AL48">
+        <v>1</v>
+      </c>
+      <c r="AM48">
+        <v>4</v>
+      </c>
+      <c r="AN48">
+        <v>7</v>
+      </c>
+      <c r="AO48">
+        <v>32</v>
+      </c>
+      <c r="AP48">
+        <v>37</v>
+      </c>
+      <c r="AQ48">
+        <v>104</v>
+      </c>
+      <c r="AR48">
+        <v>185</v>
+      </c>
+      <c r="AS48">
+        <v>133</v>
+      </c>
+      <c r="AT48">
+        <v>166</v>
+      </c>
+      <c r="AU48">
+        <v>289</v>
+      </c>
+      <c r="AV48">
+        <v>397</v>
+      </c>
+      <c r="AW48">
+        <v>492</v>
+      </c>
+      <c r="AX48">
+        <v>375</v>
+      </c>
+      <c r="AY48">
+        <v>237</v>
+      </c>
+      <c r="AZ48">
+        <v>125</v>
+      </c>
+      <c r="BA48">
+        <v>68</v>
+      </c>
+      <c r="BB48">
+        <v>23</v>
+      </c>
+      <c r="BC48">
+        <v>17</v>
+      </c>
+      <c r="BD48">
+        <v>6</v>
+      </c>
+      <c r="BE48">
+        <v>10</v>
+      </c>
+      <c r="BF48">
+        <v>1</v>
+      </c>
+      <c r="BG48">
+        <v>0</v>
+      </c>
+      <c r="BH48">
+        <v>1</v>
+      </c>
+      <c r="BI48">
+        <v>1</v>
+      </c>
+      <c r="BJ48">
+        <v>0</v>
+      </c>
+      <c r="BK48">
+        <v>1</v>
+      </c>
+      <c r="BL48">
+        <v>1</v>
+      </c>
+      <c r="BM48">
+        <v>1</v>
+      </c>
+      <c r="BN48">
         <v>0</v>
       </c>
     </row>

--- a/2026/data/GOA_arrowtooth_2026.xlsx
+++ b/2026/data/GOA_arrowtooth_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalei.shotwell\Work\GitHub\GOA-ATF-ESP\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230A647E-B345-4440-A44E-751A718EBD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C594D3-7AC1-436B-A3F8-C9E33CD4242E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="500">
   <si>
     <t>Sheet name</t>
   </si>
@@ -1550,9 +1550,6 @@
     <t>Diet_comp_weights</t>
   </si>
   <si>
-    <t>BTempC</t>
-  </si>
-  <si>
     <t>...25</t>
   </si>
   <si>
@@ -1578,6 +1575,39 @@
   </si>
   <si>
     <t>Stomach_proportion_by_weight</t>
+  </si>
+  <si>
+    <t>pred</t>
+  </si>
+  <si>
+    <t>sst</t>
+  </si>
+  <si>
+    <t>larvae</t>
+  </si>
+  <si>
+    <t>eke_east</t>
+  </si>
+  <si>
+    <t>eke_west</t>
+  </si>
+  <si>
+    <t>copepods</t>
+  </si>
+  <si>
+    <t>cond</t>
+  </si>
+  <si>
+    <t>nearshore_age1</t>
+  </si>
+  <si>
+    <t>euph</t>
+  </si>
+  <si>
+    <t>bt</t>
+  </si>
+  <si>
+    <t>lg_copepods</t>
   </si>
 </sst>
 </file>
@@ -5295,375 +5325,1907 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>1977</v>
+      </c>
+      <c r="B2">
+        <v>15248.38631</v>
+      </c>
+      <c r="C2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I2" t="s">
+        <v>478</v>
+      </c>
+      <c r="J2" t="s">
+        <v>478</v>
+      </c>
+      <c r="K2" t="s">
+        <v>478</v>
+      </c>
+      <c r="L2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1978</v>
+      </c>
+      <c r="B3">
+        <v>13659.28636</v>
+      </c>
+      <c r="C3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" t="s">
+        <v>478</v>
+      </c>
+      <c r="F3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G3" t="s">
+        <v>478</v>
+      </c>
+      <c r="H3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I3" t="s">
+        <v>478</v>
+      </c>
+      <c r="J3" t="s">
+        <v>478</v>
+      </c>
+      <c r="K3" t="s">
+        <v>478</v>
+      </c>
+      <c r="L3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>1979</v>
       </c>
-      <c r="B2">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B4">
+        <v>13105.91462</v>
+      </c>
+      <c r="C4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D4" t="s">
+        <v>478</v>
+      </c>
+      <c r="E4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F4" t="s">
+        <v>478</v>
+      </c>
+      <c r="G4" t="s">
+        <v>478</v>
+      </c>
+      <c r="H4" t="s">
+        <v>478</v>
+      </c>
+      <c r="I4" t="s">
+        <v>478</v>
+      </c>
+      <c r="J4" t="s">
+        <v>478</v>
+      </c>
+      <c r="K4" t="s">
+        <v>478</v>
+      </c>
+      <c r="L4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>1980</v>
       </c>
-      <c r="B3">
-        <v>5.03</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="B5">
+        <v>12645.50397</v>
+      </c>
+      <c r="C5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D5" t="s">
+        <v>478</v>
+      </c>
+      <c r="E5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G5" t="s">
+        <v>478</v>
+      </c>
+      <c r="H5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I5" t="s">
+        <v>478</v>
+      </c>
+      <c r="J5" t="s">
+        <v>478</v>
+      </c>
+      <c r="K5" t="s">
+        <v>478</v>
+      </c>
+      <c r="L5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>1981</v>
       </c>
-      <c r="B4">
-        <v>5.71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="B6">
+        <v>12943.0841</v>
+      </c>
+      <c r="C6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D6">
+        <v>-1.145475104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F6" t="s">
+        <v>478</v>
+      </c>
+      <c r="G6" t="s">
+        <v>478</v>
+      </c>
+      <c r="H6" t="s">
+        <v>478</v>
+      </c>
+      <c r="I6" t="s">
+        <v>478</v>
+      </c>
+      <c r="J6" t="s">
+        <v>478</v>
+      </c>
+      <c r="K6" t="s">
+        <v>478</v>
+      </c>
+      <c r="L6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>1982</v>
       </c>
-      <c r="B5">
+      <c r="B7">
+        <v>10594.435020000001</v>
+      </c>
+      <c r="C7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D7">
+        <v>-1.8218033179999999</v>
+      </c>
+      <c r="E7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F7" t="s">
+        <v>478</v>
+      </c>
+      <c r="G7" t="s">
+        <v>478</v>
+      </c>
+      <c r="H7" t="s">
+        <v>478</v>
+      </c>
+      <c r="I7" t="s">
+        <v>478</v>
+      </c>
+      <c r="J7" t="s">
+        <v>478</v>
+      </c>
+      <c r="K7" t="s">
+        <v>478</v>
+      </c>
+      <c r="L7" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1983</v>
+      </c>
+      <c r="B8">
+        <v>11659.27455</v>
+      </c>
+      <c r="C8" t="s">
+        <v>478</v>
+      </c>
+      <c r="D8">
+        <v>-0.968959299</v>
+      </c>
+      <c r="E8" t="s">
+        <v>478</v>
+      </c>
+      <c r="F8" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8" t="s">
+        <v>478</v>
+      </c>
+      <c r="H8" t="s">
+        <v>478</v>
+      </c>
+      <c r="I8" t="s">
+        <v>478</v>
+      </c>
+      <c r="J8" t="s">
+        <v>478</v>
+      </c>
+      <c r="K8" t="s">
+        <v>478</v>
+      </c>
+      <c r="L8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1984</v>
+      </c>
+      <c r="B9">
+        <v>13151.98849</v>
+      </c>
+      <c r="C9" t="s">
+        <v>478</v>
+      </c>
+      <c r="D9" t="s">
+        <v>478</v>
+      </c>
+      <c r="E9" t="s">
+        <v>478</v>
+      </c>
+      <c r="F9" t="s">
+        <v>478</v>
+      </c>
+      <c r="G9" t="s">
+        <v>478</v>
+      </c>
+      <c r="H9" t="s">
+        <v>478</v>
+      </c>
+      <c r="I9" t="s">
+        <v>478</v>
+      </c>
+      <c r="J9" t="s">
+        <v>478</v>
+      </c>
+      <c r="K9" t="s">
+        <v>478</v>
+      </c>
+      <c r="L9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1985</v>
+      </c>
+      <c r="B10">
+        <v>21351.045409999999</v>
+      </c>
+      <c r="C10">
+        <v>4.29</v>
+      </c>
+      <c r="D10">
+        <v>1.7271244160000001</v>
+      </c>
+      <c r="E10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F10" t="s">
+        <v>478</v>
+      </c>
+      <c r="G10" t="s">
+        <v>478</v>
+      </c>
+      <c r="H10" t="s">
+        <v>478</v>
+      </c>
+      <c r="I10" t="s">
+        <v>478</v>
+      </c>
+      <c r="J10" t="s">
+        <v>478</v>
+      </c>
+      <c r="K10" t="s">
+        <v>478</v>
+      </c>
+      <c r="L10" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1986</v>
+      </c>
+      <c r="B11">
+        <v>23540.14789</v>
+      </c>
+      <c r="C11">
+        <v>4.47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>478</v>
+      </c>
+      <c r="E11" t="s">
+        <v>478</v>
+      </c>
+      <c r="F11" t="s">
+        <v>478</v>
+      </c>
+      <c r="G11" t="s">
+        <v>478</v>
+      </c>
+      <c r="H11" t="s">
+        <v>478</v>
+      </c>
+      <c r="I11" t="s">
+        <v>478</v>
+      </c>
+      <c r="J11" t="s">
+        <v>478</v>
+      </c>
+      <c r="K11" t="s">
+        <v>478</v>
+      </c>
+      <c r="L11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1987</v>
+      </c>
+      <c r="B12">
+        <v>26310.234110000001</v>
+      </c>
+      <c r="C12">
+        <v>5.08</v>
+      </c>
+      <c r="D12">
+        <v>-3.3292177999999999E-2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>478</v>
+      </c>
+      <c r="F12" t="s">
+        <v>478</v>
+      </c>
+      <c r="G12" t="s">
+        <v>478</v>
+      </c>
+      <c r="H12" t="s">
+        <v>478</v>
+      </c>
+      <c r="I12" t="s">
+        <v>478</v>
+      </c>
+      <c r="J12" t="s">
+        <v>478</v>
+      </c>
+      <c r="K12" t="s">
+        <v>478</v>
+      </c>
+      <c r="L12" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1988</v>
+      </c>
+      <c r="B13">
+        <v>27358.8914</v>
+      </c>
+      <c r="C13">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="D13">
+        <v>1.2900270030000001</v>
+      </c>
+      <c r="E13" t="s">
+        <v>478</v>
+      </c>
+      <c r="F13" t="s">
+        <v>478</v>
+      </c>
+      <c r="G13" t="s">
+        <v>478</v>
+      </c>
+      <c r="H13" t="s">
+        <v>478</v>
+      </c>
+      <c r="I13" t="s">
+        <v>478</v>
+      </c>
+      <c r="J13" t="s">
+        <v>478</v>
+      </c>
+      <c r="K13" t="s">
+        <v>478</v>
+      </c>
+      <c r="L13" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1989</v>
+      </c>
+      <c r="B14">
+        <v>25061.380980000002</v>
+      </c>
+      <c r="C14">
+        <v>3.61</v>
+      </c>
+      <c r="D14">
+        <v>1.049146213</v>
+      </c>
+      <c r="E14" t="s">
+        <v>478</v>
+      </c>
+      <c r="F14" t="s">
+        <v>478</v>
+      </c>
+      <c r="G14" t="s">
+        <v>478</v>
+      </c>
+      <c r="H14" t="s">
+        <v>478</v>
+      </c>
+      <c r="I14" t="s">
+        <v>478</v>
+      </c>
+      <c r="J14" t="s">
+        <v>478</v>
+      </c>
+      <c r="K14" t="s">
+        <v>478</v>
+      </c>
+      <c r="L14" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1990</v>
+      </c>
+      <c r="B15">
+        <v>23503.43187</v>
+      </c>
+      <c r="C15">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1983</v>
-      </c>
-      <c r="B6">
-        <v>5.1100000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1984</v>
-      </c>
-      <c r="B7">
-        <v>4.7300000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1985</v>
-      </c>
-      <c r="B8">
+      <c r="D15">
+        <v>1.3385839669999999</v>
+      </c>
+      <c r="E15" t="s">
+        <v>478</v>
+      </c>
+      <c r="F15" t="s">
+        <v>478</v>
+      </c>
+      <c r="G15" t="s">
+        <v>478</v>
+      </c>
+      <c r="H15">
+        <v>1.3829039E-2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>478</v>
+      </c>
+      <c r="J15" t="s">
+        <v>478</v>
+      </c>
+      <c r="K15" t="s">
+        <v>478</v>
+      </c>
+      <c r="L15" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1991</v>
+      </c>
+      <c r="B16">
+        <v>26693.90984</v>
+      </c>
+      <c r="C16">
+        <v>3.7</v>
+      </c>
+      <c r="D16">
+        <v>0.170562924</v>
+      </c>
+      <c r="E16" t="s">
+        <v>478</v>
+      </c>
+      <c r="F16" t="s">
+        <v>478</v>
+      </c>
+      <c r="G16" t="s">
+        <v>478</v>
+      </c>
+      <c r="H16" t="s">
+        <v>478</v>
+      </c>
+      <c r="I16" t="s">
+        <v>478</v>
+      </c>
+      <c r="J16" t="s">
+        <v>478</v>
+      </c>
+      <c r="K16" t="s">
+        <v>478</v>
+      </c>
+      <c r="L16" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1992</v>
+      </c>
+      <c r="B17">
+        <v>31204.025000000001</v>
+      </c>
+      <c r="C17">
         <v>4.57</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1986</v>
-      </c>
-      <c r="B9">
-        <v>4.7300000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1987</v>
-      </c>
-      <c r="B10">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1988</v>
-      </c>
-      <c r="B11">
+      <c r="D17">
+        <v>2.041381119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>478</v>
+      </c>
+      <c r="F17" t="s">
+        <v>478</v>
+      </c>
+      <c r="G17" t="s">
+        <v>478</v>
+      </c>
+      <c r="H17" t="s">
+        <v>478</v>
+      </c>
+      <c r="I17">
+        <v>137629</v>
+      </c>
+      <c r="J17" t="s">
+        <v>478</v>
+      </c>
+      <c r="K17" t="s">
+        <v>478</v>
+      </c>
+      <c r="L17" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1993</v>
+      </c>
+      <c r="B18">
+        <v>29155.798309999998</v>
+      </c>
+      <c r="C18">
+        <v>4.2</v>
+      </c>
+      <c r="D18">
+        <v>2.6217975990000002</v>
+      </c>
+      <c r="E18">
+        <v>-34.07</v>
+      </c>
+      <c r="F18">
+        <v>-24.76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>478</v>
+      </c>
+      <c r="H18">
+        <v>1.1566763000000001E-2</v>
+      </c>
+      <c r="I18">
+        <v>11826375</v>
+      </c>
+      <c r="J18" t="s">
+        <v>478</v>
+      </c>
+      <c r="K18" t="s">
+        <v>478</v>
+      </c>
+      <c r="L18">
+        <v>5.902497576</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1994</v>
+      </c>
+      <c r="B19">
+        <v>26995.367300000002</v>
+      </c>
+      <c r="C19">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="D19">
+        <v>1.7883762050000001</v>
+      </c>
+      <c r="E19">
+        <v>-28.6</v>
+      </c>
+      <c r="F19">
+        <v>-34.590000000000003</v>
+      </c>
+      <c r="G19">
+        <v>3.09</v>
+      </c>
+      <c r="H19" t="s">
+        <v>478</v>
+      </c>
+      <c r="I19">
+        <v>3390830</v>
+      </c>
+      <c r="J19" t="s">
+        <v>478</v>
+      </c>
+      <c r="K19" t="s">
+        <v>478</v>
+      </c>
+      <c r="L19" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1995</v>
+      </c>
+      <c r="B20">
+        <v>23078.352999999999</v>
+      </c>
+      <c r="C20">
+        <v>3.99</v>
+      </c>
+      <c r="D20">
+        <v>2.2971653760000001</v>
+      </c>
+      <c r="E20">
+        <v>-8.67</v>
+      </c>
+      <c r="F20">
+        <v>-40.36</v>
+      </c>
+      <c r="G20">
+        <v>3.0529999999999999</v>
+      </c>
+      <c r="H20" t="s">
+        <v>478</v>
+      </c>
+      <c r="I20">
+        <v>3788518</v>
+      </c>
+      <c r="J20" t="s">
+        <v>478</v>
+      </c>
+      <c r="K20" t="s">
+        <v>478</v>
+      </c>
+      <c r="L20" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1996</v>
+      </c>
+      <c r="B21">
+        <v>24763.241699999999</v>
+      </c>
+      <c r="C21">
+        <v>4.32</v>
+      </c>
+      <c r="D21">
+        <v>3.1946072170000002</v>
+      </c>
+      <c r="E21">
+        <v>-23.51</v>
+      </c>
+      <c r="F21">
+        <v>-35.93</v>
+      </c>
+      <c r="G21">
+        <v>3.0310000000000001</v>
+      </c>
+      <c r="H21">
+        <v>4.24867E-4</v>
+      </c>
+      <c r="I21">
+        <v>11262967</v>
+      </c>
+      <c r="J21" t="s">
+        <v>478</v>
+      </c>
+      <c r="K21" t="s">
+        <v>478</v>
+      </c>
+      <c r="L21">
+        <v>5.5693833929999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1997</v>
+      </c>
+      <c r="B22">
+        <v>28654.26125</v>
+      </c>
+      <c r="C22">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="D22">
+        <v>2.8368044889999999</v>
+      </c>
+      <c r="E22">
+        <v>-15.56</v>
+      </c>
+      <c r="F22">
+        <v>-30.68</v>
+      </c>
+      <c r="G22" t="s">
+        <v>478</v>
+      </c>
+      <c r="H22" t="s">
+        <v>478</v>
+      </c>
+      <c r="I22">
+        <v>4124667</v>
+      </c>
+      <c r="J22" t="s">
+        <v>478</v>
+      </c>
+      <c r="K22" t="s">
+        <v>478</v>
+      </c>
+      <c r="L22" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1998</v>
+      </c>
+      <c r="B23">
+        <v>41169.819340000002</v>
+      </c>
+      <c r="C23">
+        <v>5.33</v>
+      </c>
+      <c r="D23">
+        <v>1.0035694129999999</v>
+      </c>
+      <c r="E23">
+        <v>44.75</v>
+      </c>
+      <c r="F23">
+        <v>-5</v>
+      </c>
+      <c r="G23">
+        <v>2.794</v>
+      </c>
+      <c r="H23" t="s">
+        <v>478</v>
+      </c>
+      <c r="I23">
+        <v>9035599</v>
+      </c>
+      <c r="J23" t="s">
+        <v>478</v>
+      </c>
+      <c r="K23" t="s">
+        <v>478</v>
+      </c>
+      <c r="L23" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1999</v>
+      </c>
+      <c r="B24">
+        <v>41122.258750000001</v>
+      </c>
+      <c r="C24">
+        <v>3.51</v>
+      </c>
+      <c r="D24">
+        <v>1.7581501799999999</v>
+      </c>
+      <c r="E24">
+        <v>-1.33</v>
+      </c>
+      <c r="F24">
+        <v>-40.950000000000003</v>
+      </c>
+      <c r="G24">
+        <v>2.7040000000000002</v>
+      </c>
+      <c r="H24">
+        <v>-5.1038430000000003E-3</v>
+      </c>
+      <c r="I24">
+        <v>18492742</v>
+      </c>
+      <c r="J24" t="s">
+        <v>478</v>
+      </c>
+      <c r="K24" t="s">
+        <v>478</v>
+      </c>
+      <c r="L24">
+        <v>5.0962059379999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2000</v>
+      </c>
+      <c r="B25">
+        <v>47363.523549999998</v>
+      </c>
+      <c r="C25">
+        <v>4.22</v>
+      </c>
+      <c r="D25">
+        <v>0.88124960900000004</v>
+      </c>
+      <c r="E25">
+        <v>0.34</v>
+      </c>
+      <c r="F25">
+        <v>-30.52</v>
+      </c>
+      <c r="G25">
+        <v>3.177</v>
+      </c>
+      <c r="H25" t="s">
+        <v>478</v>
+      </c>
+      <c r="I25">
+        <v>22385837</v>
+      </c>
+      <c r="J25" t="s">
+        <v>478</v>
+      </c>
+      <c r="K25">
+        <v>1.57</v>
+      </c>
+      <c r="L25" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2001</v>
+      </c>
+      <c r="B26">
+        <v>45288.103029999998</v>
+      </c>
+      <c r="C26">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="D26">
+        <v>1.550219064</v>
+      </c>
+      <c r="E26">
+        <v>16.91</v>
+      </c>
+      <c r="F26">
+        <v>-6.29</v>
+      </c>
+      <c r="G26">
+        <v>2.9209999999999998</v>
+      </c>
+      <c r="H26">
+        <v>2.3104279999999998E-3</v>
+      </c>
+      <c r="I26">
+        <v>19340020</v>
+      </c>
+      <c r="J26" t="s">
+        <v>478</v>
+      </c>
+      <c r="K26">
+        <v>1.7330000000000001</v>
+      </c>
+      <c r="L26">
+        <v>5.9022860359999996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2002</v>
+      </c>
+      <c r="B27">
+        <v>34955.136729999998</v>
+      </c>
+      <c r="C27">
+        <v>3.95</v>
+      </c>
+      <c r="D27">
+        <v>-0.35405105999999997</v>
+      </c>
+      <c r="E27">
+        <v>8.06</v>
+      </c>
+      <c r="F27">
+        <v>-18.16</v>
+      </c>
+      <c r="G27">
+        <v>2.6909999999999998</v>
+      </c>
+      <c r="H27" t="s">
+        <v>478</v>
+      </c>
+      <c r="I27">
+        <v>24663313</v>
+      </c>
+      <c r="J27" t="s">
+        <v>478</v>
+      </c>
+      <c r="K27" t="s">
+        <v>478</v>
+      </c>
+      <c r="L27" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2003</v>
+      </c>
+      <c r="B28">
+        <v>31270.472610000001</v>
+      </c>
+      <c r="C28">
+        <v>5.52</v>
+      </c>
+      <c r="D28">
+        <v>-0.35632142</v>
+      </c>
+      <c r="E28">
+        <v>51.96</v>
+      </c>
+      <c r="F28">
+        <v>29.63</v>
+      </c>
+      <c r="G28">
+        <v>3.2069999999999999</v>
+      </c>
+      <c r="H28">
+        <v>2.3443919999999998E-3</v>
+      </c>
+      <c r="I28">
+        <v>12236933</v>
+      </c>
+      <c r="J28">
+        <v>200382.74129999999</v>
+      </c>
+      <c r="K28">
+        <v>1.6759999999999999</v>
+      </c>
+      <c r="L28">
+        <v>6.102874334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2004</v>
+      </c>
+      <c r="B29">
+        <v>31996.64934</v>
+      </c>
+      <c r="C29">
+        <v>4.38</v>
+      </c>
+      <c r="D29">
+        <v>2.7210139189999998</v>
+      </c>
+      <c r="E29">
+        <v>-10.87</v>
+      </c>
+      <c r="F29">
+        <v>36.78</v>
+      </c>
+      <c r="G29">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="H29" t="s">
+        <v>478</v>
+      </c>
+      <c r="I29">
+        <v>5060913</v>
+      </c>
+      <c r="J29" t="s">
+        <v>478</v>
+      </c>
+      <c r="K29" t="s">
+        <v>478</v>
+      </c>
+      <c r="L29" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2005</v>
+      </c>
+      <c r="B30">
+        <v>37616.717830000001</v>
+      </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30">
+        <v>1.6392317940000001</v>
+      </c>
+      <c r="E30">
+        <v>-20.77</v>
+      </c>
+      <c r="F30">
+        <v>44.84</v>
+      </c>
+      <c r="G30">
+        <v>3.1</v>
+      </c>
+      <c r="H30">
+        <v>-5.931057E-3</v>
+      </c>
+      <c r="I30">
+        <v>12723811</v>
+      </c>
+      <c r="J30">
+        <v>569076.51210000005</v>
+      </c>
+      <c r="K30">
+        <v>1.6120000000000001</v>
+      </c>
+      <c r="L30">
+        <v>5.8673143230000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>2006</v>
+      </c>
+      <c r="B31">
+        <v>38903.938900000001</v>
+      </c>
+      <c r="C31">
+        <v>4.18</v>
+      </c>
+      <c r="D31">
+        <v>1.8577682849999999</v>
+      </c>
+      <c r="E31">
+        <v>-11.29</v>
+      </c>
+      <c r="F31">
+        <v>-21.67</v>
+      </c>
+      <c r="G31">
+        <v>2.9609999999999999</v>
+      </c>
+      <c r="H31" t="s">
+        <v>478</v>
+      </c>
+      <c r="I31">
+        <v>4829656</v>
+      </c>
+      <c r="J31" t="s">
+        <v>478</v>
+      </c>
+      <c r="K31" t="s">
+        <v>478</v>
+      </c>
+      <c r="L31" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>2007</v>
+      </c>
+      <c r="B32">
+        <v>33777.368210000001</v>
+      </c>
+      <c r="C32">
+        <v>3.26</v>
+      </c>
+      <c r="D32">
+        <v>1.8475412170000001</v>
+      </c>
+      <c r="E32">
+        <v>-10.58</v>
+      </c>
+      <c r="F32">
+        <v>22.93</v>
+      </c>
+      <c r="G32">
+        <v>2.6960000000000002</v>
+      </c>
+      <c r="H32">
+        <v>-6.541926E-3</v>
+      </c>
+      <c r="I32">
+        <v>19115666</v>
+      </c>
+      <c r="J32" t="s">
+        <v>478</v>
+      </c>
+      <c r="K32">
+        <v>1.399</v>
+      </c>
+      <c r="L32">
+        <v>5.0703875089999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>2008</v>
+      </c>
+      <c r="B33">
+        <v>27815.09187</v>
+      </c>
+      <c r="C33">
+        <v>3.63</v>
+      </c>
+      <c r="D33">
+        <v>0.135563507</v>
+      </c>
+      <c r="E33">
+        <v>-10.08</v>
+      </c>
+      <c r="F33">
+        <v>31.03</v>
+      </c>
+      <c r="G33">
+        <v>2.92</v>
+      </c>
+      <c r="H33" t="s">
+        <v>478</v>
+      </c>
+      <c r="I33">
+        <v>5386141</v>
+      </c>
+      <c r="J33" t="s">
+        <v>478</v>
+      </c>
+      <c r="K33" t="s">
+        <v>478</v>
+      </c>
+      <c r="L33" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>2009</v>
+      </c>
+      <c r="B34">
+        <v>20555.143349999998</v>
+      </c>
+      <c r="C34">
+        <v>3.29</v>
+      </c>
+      <c r="D34">
+        <v>-0.58334247400000006</v>
+      </c>
+      <c r="E34">
+        <v>-31.22</v>
+      </c>
+      <c r="F34">
+        <v>-34.24</v>
+      </c>
+      <c r="G34">
+        <v>2.867</v>
+      </c>
+      <c r="H34">
+        <v>-4.9044259999999999E-3</v>
+      </c>
+      <c r="I34">
+        <v>6663248</v>
+      </c>
+      <c r="J34" t="s">
+        <v>478</v>
+      </c>
+      <c r="K34">
+        <v>1.296</v>
+      </c>
+      <c r="L34">
+        <v>4.9795084379999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>2010</v>
+      </c>
+      <c r="B35">
+        <v>21421.645489999999</v>
+      </c>
+      <c r="C35">
+        <v>4.59</v>
+      </c>
+      <c r="D35">
+        <v>-0.94295863300000005</v>
+      </c>
+      <c r="E35">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="F35">
+        <v>-2.21</v>
+      </c>
+      <c r="G35">
+        <v>3.26</v>
+      </c>
+      <c r="H35" t="s">
+        <v>478</v>
+      </c>
+      <c r="I35">
+        <v>1560332</v>
+      </c>
+      <c r="J35" t="s">
+        <v>478</v>
+      </c>
+      <c r="K35" t="s">
+        <v>478</v>
+      </c>
+      <c r="L35" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>2011</v>
+      </c>
+      <c r="B36">
+        <v>19328.910479999999</v>
+      </c>
+      <c r="C36">
+        <v>4.05</v>
+      </c>
+      <c r="D36">
+        <v>1.6338793030000001</v>
+      </c>
+      <c r="E36">
+        <v>65.7</v>
+      </c>
+      <c r="F36">
+        <v>58.15</v>
+      </c>
+      <c r="G36">
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="H36">
+        <v>-5.3047739999999999E-3</v>
+      </c>
+      <c r="I36">
+        <v>5163167</v>
+      </c>
+      <c r="J36">
+        <v>620474.25989999995</v>
+      </c>
+      <c r="K36" t="s">
+        <v>478</v>
+      </c>
+      <c r="L36">
+        <v>5.4603732559999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>2012</v>
+      </c>
+      <c r="B37">
+        <v>20208.851989999999</v>
+      </c>
+      <c r="C37">
+        <v>3.33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>478</v>
+      </c>
+      <c r="E37">
+        <v>-11.88</v>
+      </c>
+      <c r="F37">
+        <v>29.63</v>
+      </c>
+      <c r="G37" t="s">
+        <v>478</v>
+      </c>
+      <c r="H37" t="s">
+        <v>478</v>
+      </c>
+      <c r="I37">
+        <v>5606338</v>
+      </c>
+      <c r="J37" t="s">
+        <v>478</v>
+      </c>
+      <c r="K37" t="s">
+        <v>478</v>
+      </c>
+      <c r="L37" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>2013</v>
+      </c>
+      <c r="B38">
+        <v>20384.51312</v>
+      </c>
+      <c r="C38">
+        <v>3.99</v>
+      </c>
+      <c r="D38">
+        <v>0.77391578100000002</v>
+      </c>
+      <c r="E38">
+        <v>-2.8</v>
+      </c>
+      <c r="F38">
+        <v>47.85</v>
+      </c>
+      <c r="G38">
+        <v>3.2879999999999998</v>
+      </c>
+      <c r="H38">
+        <v>3.0496880000000001E-3</v>
+      </c>
+      <c r="I38">
+        <v>12541222</v>
+      </c>
+      <c r="J38">
+        <v>460745.71909999999</v>
+      </c>
+      <c r="K38">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="L38">
+        <v>5.3840517229999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>2014</v>
+      </c>
+      <c r="B39">
+        <v>15213.646629999999</v>
+      </c>
+      <c r="C39">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="D39" t="s">
+        <v>478</v>
+      </c>
+      <c r="E39">
+        <v>-7.28</v>
+      </c>
+      <c r="F39">
+        <v>-21.66</v>
+      </c>
+      <c r="G39" t="s">
+        <v>478</v>
+      </c>
+      <c r="H39" t="s">
+        <v>478</v>
+      </c>
+      <c r="I39">
+        <v>22022421</v>
+      </c>
+      <c r="J39" t="s">
+        <v>478</v>
+      </c>
+      <c r="K39" t="s">
+        <v>478</v>
+      </c>
+      <c r="L39" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>2015</v>
+      </c>
+      <c r="B40">
+        <v>16698.362219999999</v>
+      </c>
+      <c r="C40">
+        <v>5.36</v>
+      </c>
+      <c r="D40">
+        <v>0.357685423</v>
+      </c>
+      <c r="E40">
+        <v>14.24</v>
+      </c>
+      <c r="F40">
+        <v>25.12</v>
+      </c>
+      <c r="G40">
+        <v>3.3370000000000002</v>
+      </c>
+      <c r="H40">
+        <v>-2.7227940000000002E-3</v>
+      </c>
+      <c r="I40">
+        <v>3607343</v>
+      </c>
+      <c r="J40">
+        <v>436759.00150000001</v>
+      </c>
+      <c r="K40">
+        <v>1.302</v>
+      </c>
+      <c r="L40">
+        <v>6.3322652210000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2016</v>
+      </c>
+      <c r="B41">
+        <v>17842.354159999999</v>
+      </c>
+      <c r="C41">
+        <v>5.81</v>
+      </c>
+      <c r="D41" t="s">
+        <v>478</v>
+      </c>
+      <c r="E41">
+        <v>19.23</v>
+      </c>
+      <c r="F41">
+        <v>36.64</v>
+      </c>
+      <c r="G41" t="s">
+        <v>478</v>
+      </c>
+      <c r="H41" t="s">
+        <v>478</v>
+      </c>
+      <c r="I41">
+        <v>3652619</v>
+      </c>
+      <c r="J41" t="s">
+        <v>478</v>
+      </c>
+      <c r="K41" t="s">
+        <v>478</v>
+      </c>
+      <c r="L41" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>2017</v>
+      </c>
+      <c r="B42">
+        <v>19040.17513</v>
+      </c>
+      <c r="C42">
+        <v>4.75</v>
+      </c>
+      <c r="D42">
+        <v>1.481673655</v>
+      </c>
+      <c r="E42">
+        <v>11.32</v>
+      </c>
+      <c r="F42">
+        <v>-28.81</v>
+      </c>
+      <c r="G42">
+        <v>3.2890000000000001</v>
+      </c>
+      <c r="H42">
+        <v>-7.7513720000000003E-3</v>
+      </c>
+      <c r="I42">
+        <v>12439171</v>
+      </c>
+      <c r="J42">
+        <v>203106.8254</v>
+      </c>
+      <c r="K42">
+        <v>1.1319999999999999</v>
+      </c>
+      <c r="L42">
+        <v>5.8954712049999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>2018</v>
+      </c>
+      <c r="B43">
+        <v>23418.206750000001</v>
+      </c>
+      <c r="C43">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1989</v>
-      </c>
-      <c r="B12">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1990</v>
-      </c>
-      <c r="B13">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1991</v>
-      </c>
-      <c r="B14">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1992</v>
-      </c>
-      <c r="B15">
-        <v>4.8899999999999997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1993</v>
-      </c>
-      <c r="B16">
-        <v>4.5199999999999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1994</v>
-      </c>
-      <c r="B17">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1995</v>
-      </c>
-      <c r="B18">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1996</v>
-      </c>
-      <c r="B19">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1997</v>
-      </c>
-      <c r="B20">
-        <v>4.5599999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1998</v>
-      </c>
-      <c r="B21">
-        <v>5.73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>1999</v>
-      </c>
-      <c r="B22">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>2000</v>
-      </c>
-      <c r="B23">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>2001</v>
-      </c>
-      <c r="B24">
-        <v>4.9800000000000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>2002</v>
-      </c>
-      <c r="B25">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>2003</v>
-      </c>
-      <c r="B26">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>2004</v>
-      </c>
-      <c r="B27">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>2005</v>
-      </c>
-      <c r="B28">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>2006</v>
-      </c>
-      <c r="B29">
-        <v>4.63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>2007</v>
-      </c>
-      <c r="B30">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>2008</v>
-      </c>
-      <c r="B31">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>2009</v>
-      </c>
-      <c r="B32">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>2010</v>
-      </c>
-      <c r="B33">
-        <v>5.21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>2011</v>
-      </c>
-      <c r="B34">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>2012</v>
-      </c>
-      <c r="B35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>2013</v>
-      </c>
-      <c r="B36">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>2014</v>
-      </c>
-      <c r="B37">
-        <v>4.7300000000000004</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>2015</v>
-      </c>
-      <c r="B38">
-        <v>5.88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>2016</v>
-      </c>
-      <c r="B39">
-        <v>5.71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>2017</v>
-      </c>
-      <c r="B40">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>2018</v>
-      </c>
-      <c r="B41">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="D43" t="s">
+        <v>478</v>
+      </c>
+      <c r="E43">
+        <v>26.34</v>
+      </c>
+      <c r="F43">
+        <v>-31.62</v>
+      </c>
+      <c r="G43" t="s">
+        <v>478</v>
+      </c>
+      <c r="H43" t="s">
+        <v>478</v>
+      </c>
+      <c r="I43">
+        <v>8283740</v>
+      </c>
+      <c r="J43" t="s">
+        <v>478</v>
+      </c>
+      <c r="K43" t="s">
+        <v>478</v>
+      </c>
+      <c r="L43" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>2019</v>
       </c>
-      <c r="B42">
-        <v>5.94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="B44">
+        <v>23642.562190000001</v>
+      </c>
+      <c r="C44">
+        <v>5.62</v>
+      </c>
+      <c r="D44">
+        <v>-0.172489369</v>
+      </c>
+      <c r="E44">
+        <v>5.46</v>
+      </c>
+      <c r="F44">
+        <v>-10.67</v>
+      </c>
+      <c r="G44">
+        <v>3.3559999999999999</v>
+      </c>
+      <c r="H44">
+        <v>4.349693E-3</v>
+      </c>
+      <c r="I44">
+        <v>10544652</v>
+      </c>
+      <c r="J44">
+        <v>336170</v>
+      </c>
+      <c r="K44">
+        <v>1.4970000000000001</v>
+      </c>
+      <c r="L44">
+        <v>6.3910258850000004</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>2020</v>
       </c>
-      <c r="B43">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="B45">
+        <v>19194.74266</v>
+      </c>
+      <c r="C45">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="D45" t="s">
+        <v>478</v>
+      </c>
+      <c r="E45">
+        <v>-40.39</v>
+      </c>
+      <c r="F45">
+        <v>17.510000000000002</v>
+      </c>
+      <c r="G45" t="s">
+        <v>478</v>
+      </c>
+      <c r="H45" t="s">
+        <v>478</v>
+      </c>
+      <c r="I45">
+        <v>6933691</v>
+      </c>
+      <c r="J45" t="s">
+        <v>478</v>
+      </c>
+      <c r="K45" t="s">
+        <v>478</v>
+      </c>
+      <c r="L45" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>2021</v>
       </c>
-      <c r="B44">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="B46">
+        <v>17110.174879999999</v>
+      </c>
+      <c r="C46">
+        <v>4.53</v>
+      </c>
+      <c r="D46">
+        <v>1.235706875</v>
+      </c>
+      <c r="E46">
+        <v>-6.82</v>
+      </c>
+      <c r="F46">
+        <v>44.66</v>
+      </c>
+      <c r="G46">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="H46">
+        <v>3.10428E-5</v>
+      </c>
+      <c r="I46">
+        <v>3500029</v>
+      </c>
+      <c r="J46" t="s">
+        <v>478</v>
+      </c>
+      <c r="K46" t="s">
+        <v>478</v>
+      </c>
+      <c r="L46">
+        <v>5.7438771109999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>2022</v>
       </c>
-      <c r="B45">
-        <v>5.09</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="B47">
+        <v>19188.285739999999</v>
+      </c>
+      <c r="C47">
+        <v>4.32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>478</v>
+      </c>
+      <c r="E47">
+        <v>-7.79</v>
+      </c>
+      <c r="F47">
+        <v>-9.86</v>
+      </c>
+      <c r="G47" t="s">
+        <v>478</v>
+      </c>
+      <c r="H47" t="s">
+        <v>478</v>
+      </c>
+      <c r="I47">
+        <v>2551866</v>
+      </c>
+      <c r="J47" t="s">
+        <v>478</v>
+      </c>
+      <c r="K47" t="s">
+        <v>478</v>
+      </c>
+      <c r="L47" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>2023</v>
       </c>
-      <c r="B46">
-        <v>4.4400000000000004</v>
+      <c r="B48">
+        <v>18865.697230000002</v>
+      </c>
+      <c r="C48">
+        <v>4.22</v>
+      </c>
+      <c r="D48">
+        <v>1.741747624</v>
+      </c>
+      <c r="E48">
+        <v>-12.28</v>
+      </c>
+      <c r="F48">
+        <v>-27.3</v>
+      </c>
+      <c r="G48">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="H48">
+        <v>9.2136499999999994E-5</v>
+      </c>
+      <c r="I48">
+        <v>4085143</v>
+      </c>
+      <c r="J48" t="s">
+        <v>478</v>
+      </c>
+      <c r="K48">
+        <v>1.677</v>
+      </c>
+      <c r="L48">
+        <v>5.477908824</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>2024</v>
+      </c>
+      <c r="B49">
+        <v>20266.09302</v>
+      </c>
+      <c r="C49">
+        <v>4.54</v>
+      </c>
+      <c r="D49" t="s">
+        <v>478</v>
+      </c>
+      <c r="E49">
+        <v>15.53</v>
+      </c>
+      <c r="F49">
+        <v>48.45</v>
+      </c>
+      <c r="G49" t="s">
+        <v>478</v>
+      </c>
+      <c r="H49" t="s">
+        <v>478</v>
+      </c>
+      <c r="I49">
+        <v>2066137</v>
+      </c>
+      <c r="J49" t="s">
+        <v>478</v>
+      </c>
+      <c r="K49" t="s">
+        <v>478</v>
+      </c>
+      <c r="L49" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>2025</v>
+      </c>
+      <c r="B50">
+        <v>20973.38492</v>
+      </c>
+      <c r="C50">
+        <v>5.16</v>
+      </c>
+      <c r="D50">
+        <v>-1.6934433</v>
+      </c>
+      <c r="E50">
+        <v>-3.38</v>
+      </c>
+      <c r="F50">
+        <v>-23.61</v>
+      </c>
+      <c r="G50" t="s">
+        <v>478</v>
+      </c>
+      <c r="H50">
+        <v>-2.0086099999999999E-4</v>
+      </c>
+      <c r="I50">
+        <v>3698795</v>
+      </c>
+      <c r="J50" t="s">
+        <v>478</v>
+      </c>
+      <c r="K50" t="s">
+        <v>478</v>
+      </c>
+      <c r="L50">
+        <v>6.1345535269999996</v>
       </c>
     </row>
   </sheetData>
@@ -5750,10 +7312,10 @@
         <v>303</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>468</v>
@@ -5937,22 +7499,22 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>153</v>
@@ -5961,7 +7523,7 @@
         <v>162</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">

--- a/2026/data/GOA_arrowtooth_2026.xlsx
+++ b/2026/data/GOA_arrowtooth_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C594D3-7AC1-436B-A3F8-C9E33CD4242E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>

--- a/2026/data/GOA_arrowtooth_2026.xlsx
+++ b/2026/data/GOA_arrowtooth_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalei.shotwell\Work\GitHub\GOA-ATF-ESP\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91885FDE-C63D-46DE-BD6A-7B4FB17E164A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7178123F-A3A1-40A7-B288-8A1EC230E66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2568" yWindow="1920" windowWidth="26136" windowHeight="13704" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>
@@ -61073,7 +61073,7 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>12621.795976890819</v>
+        <v>16834.943039591308</v>
       </c>
       <c r="H51">
         <v>0.05</v>

--- a/2026/data/GOA_arrowtooth_2026.xlsx
+++ b/2026/data/GOA_arrowtooth_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kalei.shotwell\Work\GitHub\GOA-ATF-ESP\2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7178123F-A3A1-40A7-B288-8A1EC230E66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB61D98-EFB9-49B9-A0FB-2F05349C94E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2568" yWindow="1920" windowWidth="26136" windowHeight="13704" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31596" yWindow="744" windowWidth="26136" windowHeight="13704" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta_data" sheetId="1" r:id="rId1"/>
@@ -59121,7 +59121,7 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>0.1188226</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
@@ -59186,7 +59186,7 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.1188226</v>
+        <v>0.1173554</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
